--- a/models/Misr-Fertilizers-MFPC-Valuation-Model.xlsx
+++ b/models/Misr-Fertilizers-MFPC-Valuation-Model.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\7\MFPC - CA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Portfolio\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF86FFD5-4131-456B-9713-1632BBE61D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BE1731-6364-4768-AB6B-E363E2A9AED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="646" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="646" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FSM" sheetId="1" r:id="rId1"/>
     <sheet name="DCF" sheetId="2" r:id="rId2"/>
     <sheet name="WACC" sheetId="3" r:id="rId3"/>
-    <sheet name="Trading Comps &quot;Subjective&quot;" sheetId="7" r:id="rId4"/>
-    <sheet name="Transaction Comps" sheetId="5" r:id="rId5"/>
-    <sheet name="Accretion Dilution" sheetId="6" r:id="rId6"/>
-    <sheet name="Trading Comps" sheetId="4" r:id="rId7"/>
+    <sheet name="Trading Comps" sheetId="7" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="CIQWBGuid" localSheetId="1" hidden="1">"DCF_complete.xlsx"</definedName>
@@ -673,114 +670,8 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Ahmed Wael</author>
-  </authors>
-  <commentList>
-    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{084DF4AC-79F0-4A4D-93BF-0DB410A5B5E4}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ahmed Wael:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-$3.62bn for OCI's 50.8% (completed Oct-2024). Implied 100% equity $7.13bn + ND $1.04bn = TV $8.17bn.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F21" authorId="0" shapeId="0" xr:uid="{03DC3E35-C964-4604-B401-8B964B135C6B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ahmed Wael:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Pre-revenue project under construction — multiples Not Meaningful. Asset deals are valued on capacity/replacement cost, not earnings.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{C5D7AE47-BDAA-41A3-8489-721A549D8C08}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ahmed Wael:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-2024 EBITDA at announcement (trough year — inflates multiple to 12.6x). Verify from Fertiglobe FY24 release.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F22" authorId="0" shapeId="0" xr:uid="{5E11A758-FDA9-44C1-9B88-404801412EAB}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ahmed Wael:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Pre-revenue project under construction — multiples Not Meaningful. Asset deals are valued on capacity/replacement cost, not earnings.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="382">
   <si>
     <t>Discounted Cash Flow Valuation</t>
   </si>
@@ -1892,9 +1783,6 @@
     <t>Peer median EV/EBITDA</t>
   </si>
   <si>
-    <t>x MOPCO LTM EBITDA</t>
-  </si>
-  <si>
     <t>Implied Enterprise Value</t>
   </si>
   <si>
@@ -1922,456 +1810,6 @@
     <t>ABUK EV/EBITDA</t>
   </si>
   <si>
-    <t>GENERAL TRANSACTION INFORMATION</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Fertiglobe (50.8%)</t>
-  </si>
-  <si>
-    <t>Iowa Fertilizer Co.</t>
-  </si>
-  <si>
-    <t>OCI Clean Ammonia</t>
-  </si>
-  <si>
-    <t>MOPCO (20%)</t>
-  </si>
-  <si>
-    <t>Acquirer</t>
-  </si>
-  <si>
-    <t>ADNOC (XRG)</t>
-  </si>
-  <si>
-    <t>Koch Ag &amp; Energy</t>
-  </si>
-  <si>
-    <t>Woodside Energy</t>
-  </si>
-  <si>
-    <t>ADQ (Alfa Oryx)</t>
-  </si>
-  <si>
-    <t>Seller</t>
-  </si>
-  <si>
-    <t>OCI Global</t>
-  </si>
-  <si>
-    <t>Market / block trade</t>
-  </si>
-  <si>
-    <t>Announcement date</t>
-  </si>
-  <si>
-    <t>Sep-2024</t>
-  </si>
-  <si>
-    <t>Dec-2023</t>
-  </si>
-  <si>
-    <t>Aug-2024</t>
-  </si>
-  <si>
-    <t>Apr-2022</t>
-  </si>
-  <si>
-    <t>Deal status</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>% of target acquired</t>
-  </si>
-  <si>
-    <t>Control acquired?</t>
-  </si>
-  <si>
-    <t>Yes (majority)</t>
-  </si>
-  <si>
-    <t>Yes (100%)</t>
-  </si>
-  <si>
-    <t>No (minority)</t>
-  </si>
-  <si>
-    <t>OFFER &amp; TRANSACTION VALUE (USD mn)</t>
-  </si>
-  <si>
-    <t>Consideration paid for stake</t>
-  </si>
-  <si>
-    <t>Implied 100% equity value</t>
-  </si>
-  <si>
-    <t>Net debt / (cash) at deal</t>
-  </si>
-  <si>
-    <t>Transaction value (TV = implied EV)</t>
-  </si>
-  <si>
-    <t>TARGET LTM FINANCIALS AT ANNOUNCEMENT (USD mn)</t>
-  </si>
-  <si>
-    <t>LTM revenue</t>
-  </si>
-  <si>
-    <t>NM</t>
-  </si>
-  <si>
-    <t>LTM EBITDA</t>
-  </si>
-  <si>
-    <t>TRANSACTION MULTIPLES</t>
-  </si>
-  <si>
-    <t>TV / LTM Revenue</t>
-  </si>
-  <si>
-    <t>TV / LTM EBITDA</t>
-  </si>
-  <si>
-    <t>DEAL STATISTICS</t>
-  </si>
-  <si>
-    <t>TV/Revenue</t>
-  </si>
-  <si>
-    <t>TV/EBITDA</t>
-  </si>
-  <si>
-    <t>IMPLIED MOPCO VALUATION — CONTROL BASIS (EGP mn)</t>
-  </si>
-  <si>
-    <t>Median TV/EBITDA (precedent deals)</t>
-  </si>
-  <si>
-    <t>x MOPCO LTM EBITDA (EGP mn)</t>
-  </si>
-  <si>
-    <t>Implied EV</t>
-  </si>
-  <si>
-    <t>Plus: net cash</t>
-  </si>
-  <si>
-    <t>Accretion / (Dilution) Analysis — Illustrative: MOPCO acquires Abu Qir Fertilizers (ABUK)</t>
-  </si>
-  <si>
-    <t>EGP in millions, except per share | Hypothetical consolidation of Egyptian nitrogen — for technical demonstration only | Year 1 = FY2026E</t>
-  </si>
-  <si>
-    <t>BLUE = input | GREEN = link (FSM / DCF / Trading Comps) | YELLOW = estimate, VERIFY</t>
-  </si>
-  <si>
-    <t>TRANSACTION ASSUMPTIONS</t>
-  </si>
-  <si>
-    <t>SOURCES &amp; USES OF FUNDS (EGP mn)</t>
-  </si>
-  <si>
-    <t>Acquirer: MOPCO (MFPC.CA)</t>
-  </si>
-  <si>
-    <t>Sources</t>
-  </si>
-  <si>
-    <t>Share price (EGP)</t>
-  </si>
-  <si>
-    <t>New debt raised</t>
-  </si>
-  <si>
-    <t>Diluted shares outstanding (mn)</t>
-  </si>
-  <si>
-    <t>Excess cash used</t>
-  </si>
-  <si>
-    <t>FY2026E net income (EGP mn)</t>
-  </si>
-  <si>
-    <t>Stock issued to target shareholders</t>
-  </si>
-  <si>
-    <t>Standalone FY2026E EPS</t>
-  </si>
-  <si>
-    <t>Cash for fees</t>
-  </si>
-  <si>
-    <t>Acquirer tax rate</t>
-  </si>
-  <si>
-    <t>Total sources</t>
-  </si>
-  <si>
-    <t>Available cash + liquid investments (EGP mn)</t>
-  </si>
-  <si>
-    <t>Uses</t>
-  </si>
-  <si>
-    <t>Equity purchase price (cash portion)</t>
-  </si>
-  <si>
-    <t>Target: Abu Qir Fertilizers (ABUK.CA)</t>
-  </si>
-  <si>
-    <t>Equity purchase price (stock portion)</t>
-  </si>
-  <si>
-    <t>Current share price (EGP)</t>
-  </si>
-  <si>
-    <t>Deal fees</t>
-  </si>
-  <si>
-    <t>% offer premium</t>
-  </si>
-  <si>
-    <t>Financing fees</t>
-  </si>
-  <si>
-    <t>Offer price per share</t>
-  </si>
-  <si>
-    <t>Total uses</t>
-  </si>
-  <si>
-    <t>Target diluted shares (mn)</t>
-  </si>
-  <si>
-    <t>Sources = Uses?</t>
-  </si>
-  <si>
-    <t>Offer value / equity purchase price</t>
-  </si>
-  <si>
-    <t>% of MOPCO cash pile consumed</t>
-  </si>
-  <si>
-    <t>Target FY1 net income (proxy = LTM, EGP mn)</t>
-  </si>
-  <si>
-    <t>Ideally use ABUK FY2026E consensus / your own forecast — LTM used as proxy, flag it</t>
-  </si>
-  <si>
-    <t>Target P/E paid (offer value / target NI)</t>
-  </si>
-  <si>
-    <t>PURCHASE PRICE ALLOCATION &amp; GOODWILL (EGP mn)</t>
-  </si>
-  <si>
-    <t>Target book value of equity</t>
-  </si>
-  <si>
-    <t>ABUK: assets 40.1bn - liabilities 7.5bn (latest reported) — VERIFY from FY24/25 FS</t>
-  </si>
-  <si>
-    <t>Deal structure &amp; financing</t>
-  </si>
-  <si>
-    <t>PP&amp;E write-up (%)</t>
-  </si>
-  <si>
-    <t>% stock consideration</t>
-  </si>
-  <si>
-    <t>Target PP&amp;E book value</t>
-  </si>
-  <si>
-    <t>% cash consideration</t>
-  </si>
-  <si>
-    <t>PP&amp;E write-up amount</t>
-  </si>
-  <si>
-    <t>% of cash portion financed with NEW DEBT</t>
-  </si>
-  <si>
-    <t>Useful life (years)</t>
-  </si>
-  <si>
-    <t>% of cash portion from EXCESS CASH</t>
-  </si>
-  <si>
-    <t>Incremental annual depreciation</t>
-  </si>
-  <si>
-    <t>Interest rate on new EGP debt</t>
-  </si>
-  <si>
-    <t>DTL created on write-up (share deal, no tax step-up)</t>
-  </si>
-  <si>
-    <t>CBE lending 22% (Note 36) + corporate spread — VERIFY current bank pricing</t>
-  </si>
-  <si>
-    <t>Interest earned on cash (opportunity cost)</t>
-  </si>
-  <si>
-    <t>Goodwill = offer value - (book equity + write-up - DTL)</t>
-  </si>
-  <si>
-    <t>MOPCO effective yield on its treasury portfolio (FSM interest schedule) — cash is NOT free in Egypt</t>
-  </si>
-  <si>
-    <t>Annual pretax cost synergies (EGP mn)</t>
-  </si>
-  <si>
-    <t>Goodwill created</t>
-  </si>
-  <si>
-    <t>Illustrative: procurement, logistics, SG&amp;A overlap — defend as ~0.7% of combined COGS</t>
-  </si>
-  <si>
-    <t>Deal fees (% of offer value, expensed one-time)</t>
-  </si>
-  <si>
-    <t>Financing fees (% of new debt, amortized 5 yrs)</t>
-  </si>
-  <si>
-    <t>ACCRETION / (DILUTION) — YEAR 1 (FY2026E, EGP mn)</t>
-  </si>
-  <si>
-    <t>Acquirer net income (standalone)</t>
-  </si>
-  <si>
-    <t>Exchange ratios</t>
-  </si>
-  <si>
-    <t>Target net income</t>
-  </si>
-  <si>
-    <t>New MOPCO shares issued (mn)</t>
-  </si>
-  <si>
-    <t>Transaction adjustments (pretax):</t>
-  </si>
-  <si>
-    <t>Nominal exchange ratio (offer / MOPCO price)</t>
-  </si>
-  <si>
-    <t>Less: interest on new debt</t>
-  </si>
-  <si>
-    <t>Actual exchange ratio (% stock x offer / MOPCO price)</t>
-  </si>
-  <si>
-    <t>Less: interest income forgone on cash used</t>
-  </si>
-  <si>
-    <t>Plus: pretax synergies</t>
-  </si>
-  <si>
-    <t>Less: incremental depreciation (write-up)</t>
-  </si>
-  <si>
-    <t>Less: financing fee amortization</t>
-  </si>
-  <si>
-    <t>Tax effect (at acquirer rate)</t>
-  </si>
-  <si>
-    <t>Total after-tax adjustments</t>
-  </si>
-  <si>
-    <t>Pro forma net income</t>
-  </si>
-  <si>
-    <t>Pro forma shares (acquirer + new shares)</t>
-  </si>
-  <si>
-    <t>Pro forma EPS</t>
-  </si>
-  <si>
-    <t>Acquirer standalone EPS</t>
-  </si>
-  <si>
-    <t>Accretion / (dilution) per share</t>
-  </si>
-  <si>
-    <t>Accretion / (dilution) %</t>
-  </si>
-  <si>
-    <t>Pretax synergies required to break even</t>
-  </si>
-  <si>
-    <t>CONTRIBUTION ANALYSIS (sanity check on deal fairness)</t>
-  </si>
-  <si>
-    <t>MOPCO</t>
-  </si>
-  <si>
-    <t>ABUK</t>
-  </si>
-  <si>
-    <t>Revenue contribution</t>
-  </si>
-  <si>
-    <t>EBITDA contribution</t>
-  </si>
-  <si>
-    <t>Net income contribution</t>
-  </si>
-  <si>
-    <t>Pro forma ownership (MOPCO holders vs ABUK holders)</t>
-  </si>
-  <si>
-    <t>If ABUK contributes ~45% of profit but gets this ownership % + cash, compare value received vs contributed.</t>
-  </si>
-  <si>
-    <t>SENSITIVITY: YEAR-1 ACCRETION/(DILUTION) % — % STOCK vs OFFER PREMIUM</t>
-  </si>
-  <si>
-    <t>% stock \ premium</t>
-  </si>
-  <si>
-    <t>SENSITIVITY ENGINE (each row = one grid cell)</t>
-  </si>
-  <si>
-    <t>Engine columns L:U show every intermediate step per scenario — full transparency, no black-box data tables.</t>
-  </si>
-  <si>
-    <t>NOTES &amp; KEY JUDGMENTS</t>
-  </si>
-  <si>
-    <t>Illustrative transaction for technical demonstration — no deal is announced or implied. Target FY1 NI uses LTM as proxy (yellow).</t>
-  </si>
-  <si>
-    <t>Egypt twist vs the classic US intuition: with EGP rates ~20%+, cash is NOT cheap. After-tax cost of debt ~18.6% and forgone yield on cash ~12.9% vs target earnings yield (1/P/E paid) ~8-9% -&gt; cash-funded portions are DILUTIVE here, unlike low-rate markets.</t>
-  </si>
-  <si>
-    <t>Stock portion: MOPCO P/E ~9.1x buying ABUK at ~11.9x paid (25% premium) -&gt; issuing 'cheaper' paper for 'more expensive' earnings = dilutive. Rule: stock deals dilute when acquirer P/E &lt; P/E paid.</t>
-  </si>
-  <si>
-    <t>Both levers point the same way, so the base case is dilutive and the breakeven-synergies line quantifies the gap - that is the honest analytical answer, not a failure of the model.</t>
-  </si>
-  <si>
-    <t>PPA: share acquisition in Egypt = no tax step-up -&gt; DTL on the write-up; incremental depreciation is book-only. Goodwill is not amortized under EAS/IFRS - tested annually for impairment.</t>
-  </si>
-  <si>
-    <t>One-time deal fees are excluded from run-rate EPS (expensed at close); only recurring items (interest, synergies, incremental D&amp;A, financing fee amortization) drive Year-1 accretion.</t>
-  </si>
-  <si>
-    <t>Verify yellow cells: ABUK book equity &amp; PP&amp;E from its FY24/25 FS; debt pricing from current bank quotes.</t>
-  </si>
-  <si>
-    <t>USD in millions unless noted | MENA nitrogen fertilizer M&amp;A</t>
-  </si>
-  <si>
-    <t>Each company in its LOCAL currency, millions (multiples are currency-independent)</t>
-  </si>
-  <si>
-    <t>Fertiglobe: price converted to USD (AED 3.05 / 3.6725 peg) to match USD financials</t>
-  </si>
-  <si>
     <t>x LTM EBITDA</t>
   </si>
   <si>
@@ -2379,54 +1817,48 @@
   </si>
   <si>
     <t>Comparable Companies Analysis (Trading Comps)</t>
-  </si>
-  <si>
-    <t>Precedent Transactions Analysis (Transaction Comps)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="39">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="&quot;FY&quot;yy"/>
-    <numFmt numFmtId="168" formatCode="0\A;[Red]0\A"/>
-    <numFmt numFmtId="169" formatCode="0\P_);\(0\P\)"/>
-    <numFmt numFmtId="170" formatCode="m/d/yy;@"/>
-    <numFmt numFmtId="171" formatCode="0.0%_);\(0.0%\);@_)"/>
-    <numFmt numFmtId="172" formatCode="_(#,##0.0%_);\(#,##0.0%\);_(&quot;–&quot;_)_%;_(@_)_%"/>
-    <numFmt numFmtId="173" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="174" formatCode="#,##0_);\(#,##0\);@_)"/>
-    <numFmt numFmtId="175" formatCode="0000\P"/>
-    <numFmt numFmtId="176" formatCode="0.0\x_);\(0.0\x\);@_)"/>
-    <numFmt numFmtId="177" formatCode="0.000%_);\(0.000%\);@_)"/>
-    <numFmt numFmtId="178" formatCode="#,##0.000_);\(#,##0.000\);@_)"/>
-    <numFmt numFmtId="179" formatCode="#,##0.000_);\(#,##0.000\)"/>
-    <numFmt numFmtId="180" formatCode="_([$$]#,##0_)_%;\([$$]#,##0\)_%;_(&quot;–&quot;_)_%;_(@_)_%"/>
-    <numFmt numFmtId="181" formatCode="_(0.0_)_'_x;_(\(0.0\)_';_(&quot;–&quot;_)_%;_(@_)_%"/>
-    <numFmt numFmtId="182" formatCode="#,##0.00_);\(#,##0.00\);\-_);@_)"/>
-    <numFmt numFmtId="183" formatCode="#,##0.0_);\(#,##0.0\);\-_);@_)"/>
-    <numFmt numFmtId="184" formatCode="_(#,##0.00%_);\(#,##0.00%\);_(&quot;–&quot;_)_%;_(@_)_%"/>
-    <numFmt numFmtId="185" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\);@_)"/>
-    <numFmt numFmtId="186" formatCode="0000\A"/>
-    <numFmt numFmtId="187" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* \-??_);_(@_)"/>
-    <numFmt numFmtId="188" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="189" formatCode="d/m/yy;@"/>
-    <numFmt numFmtId="190" formatCode="_(0.0\x_)_';_(\(0.0\x\)_';_(&quot;–&quot;_)_%;_(@_)_%"/>
-    <numFmt numFmtId="191" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
-    <numFmt numFmtId="192" formatCode="0.000"/>
-    <numFmt numFmtId="193" formatCode="#,##0.00_);\(#,##0.00\)"/>
+  <numFmts count="36">
+    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="&quot;FY&quot;yy"/>
+    <numFmt numFmtId="170" formatCode="0\A;[Red]0\A"/>
+    <numFmt numFmtId="171" formatCode="0\P_);\(0\P\)"/>
+    <numFmt numFmtId="172" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="173" formatCode="0.0%_);\(0.0%\);@_)"/>
+    <numFmt numFmtId="174" formatCode="_(#,##0.0%_);\(#,##0.0%\);_(&quot;–&quot;_)_%;_(@_)_%"/>
+    <numFmt numFmtId="175" formatCode="#,##0_);\(#,##0\);@_)"/>
+    <numFmt numFmtId="176" formatCode="0000\P"/>
+    <numFmt numFmtId="177" formatCode="0.0\x_);\(0.0\x\);@_)"/>
+    <numFmt numFmtId="178" formatCode="0.000%_);\(0.000%\);@_)"/>
+    <numFmt numFmtId="179" formatCode="#,##0.000_);\(#,##0.000\);@_)"/>
+    <numFmt numFmtId="180" formatCode="#,##0.000_);\(#,##0.000\)"/>
+    <numFmt numFmtId="181" formatCode="_([$$]#,##0_)_%;\([$$]#,##0\)_%;_(&quot;–&quot;_)_%;_(@_)_%"/>
+    <numFmt numFmtId="182" formatCode="_(0.0_)_'_x;_(\(0.0\)_';_(&quot;–&quot;_)_%;_(@_)_%"/>
+    <numFmt numFmtId="183" formatCode="#,##0.00_);\(#,##0.00\);\-_);@_)"/>
+    <numFmt numFmtId="184" formatCode="#,##0.0_);\(#,##0.0\);\-_);@_)"/>
+    <numFmt numFmtId="185" formatCode="_(#,##0.00%_);\(#,##0.00%\);_(&quot;–&quot;_)_%;_(@_)_%"/>
+    <numFmt numFmtId="186" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\);@_)"/>
+    <numFmt numFmtId="187" formatCode="0000\A"/>
+    <numFmt numFmtId="188" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* \-??_);_(@_)"/>
+    <numFmt numFmtId="189" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="190" formatCode="d/m/yy;@"/>
+    <numFmt numFmtId="191" formatCode="_(0.0\x_)_';_(\(0.0\x\)_';_(&quot;–&quot;_)_%;_(@_)_%"/>
+    <numFmt numFmtId="192" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
+    <numFmt numFmtId="193" formatCode="0.000"/>
     <numFmt numFmtId="194" formatCode="_-[$EGP]\ * #,##0.00_-;\-[$EGP]\ * #,##0.00_-;_-[$EGP]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="195" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="196" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="197" formatCode="0.0&quot;x&quot;"/>
-    <numFmt numFmtId="198" formatCode="#,##0.00;\(#,##0.00\)"/>
-    <numFmt numFmtId="199" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="200" formatCode="[$-409]mmmmm/yy;@"/>
   </numFmts>
   <fonts count="46" x14ac:knownFonts="1">
@@ -2750,7 +2182,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2779,16 +2211,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC9DAF8"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -3153,16 +2575,16 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="191" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="192" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="37" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="200" fontId="33" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="327">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3177,47 +2599,47 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
@@ -3226,18 +2648,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyBorder="1"/>
@@ -3245,7 +2667,7 @@
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="22" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3253,13 +2675,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="5"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="22" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="7" fontId="22" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyBorder="1"/>
-    <xf numFmtId="173" fontId="22" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="7" fontId="22" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -3272,38 +2694,38 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="22" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="22" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="174" fontId="26" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="22" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="25" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="22" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="25" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="172" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3315,8 +2737,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="22" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -3324,19 +2746,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="28" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="28" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="19" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3345,7 +2767,7 @@
     <xf numFmtId="37" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
@@ -3364,27 +2786,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="9" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="184" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="9" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="185" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3394,7 +2816,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="3" applyBorder="1"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3405,28 +2827,28 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="185" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="9" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyBorder="1"/>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="30" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="30" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -3440,19 +2862,19 @@
     <xf numFmtId="39" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="39" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="7" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="22" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="187" fontId="7" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="22" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="21" xfId="2" applyBorder="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="26" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="22" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="20" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3460,59 +2882,59 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="188" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="188" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="9" fontId="32" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="37" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="30" fillId="3" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="30" fillId="3" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3524,89 +2946,89 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="189" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="190" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="35" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="35" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="190" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="32" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="38" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="185" fontId="38" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="191" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="192" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="37" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3615,13 +3037,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="192" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="192" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="193" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="193" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3633,7 +3055,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3644,14 +3066,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="37" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="193" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="39" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="193" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="39" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="194" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -3664,7 +3084,7 @@
     <xf numFmtId="194" fontId="39" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
@@ -3673,7 +3093,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="22" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="22" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3681,7 +3101,6 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="196" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="196" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="196" fontId="16" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -3696,25 +3115,7 @@
     <xf numFmtId="195" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="195" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="196" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="198" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="198" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="196" fontId="45" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="199" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="196" fontId="35" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="35" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="198" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="16" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="196" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -4786,7 +4187,7 @@
       <c r="C7" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="303">
+      <c r="D7" s="301">
         <v>36</v>
       </c>
     </row>
@@ -8280,7 +7681,7 @@
       <c r="C143" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="D143" s="305">
+      <c r="D143" s="303">
         <v>1174057956</v>
       </c>
       <c r="E143" s="185">
@@ -12540,7 +11941,7 @@
       <c r="F5" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="302">
+      <c r="H5" s="300">
         <v>36</v>
       </c>
     </row>
@@ -12573,14 +11974,14 @@
         <v>9</v>
       </c>
       <c r="G7" s="59"/>
-      <c r="H7" s="301">
+      <c r="H7" s="299">
         <f>C73</f>
         <v>32.019767144702811</v>
       </c>
-      <c r="I7" s="304" t="s">
+      <c r="I7" s="302" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="311"/>
+      <c r="K7" s="309"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="51" t="s">
@@ -12598,7 +11999,7 @@
         <f>H7/H5-1</f>
         <v>-0.11056202375825519</v>
       </c>
-      <c r="I8" s="306" t="str">
+      <c r="I8" s="304" t="str">
         <f t="array" ref="I8">_xlfn.IFS(H8&gt;15%,"BUY",H8&gt;=0,"HOLD",H8&lt;0,"SELL")</f>
         <v>SELL</v>
       </c>
@@ -13743,11 +13144,11 @@
       <c r="B73" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="C73" s="301">
+      <c r="C73" s="299">
         <f>C71/C72</f>
         <v>32.019767144702811</v>
       </c>
-      <c r="D73" s="301">
+      <c r="D73" s="299">
         <f>D71/D72</f>
         <v>31.287366110404825</v>
       </c>
@@ -14840,7 +14241,7 @@
       <c r="B6" s="51" t="s">
         <v>287</v>
       </c>
-      <c r="C6" s="310">
+      <c r="C6" s="308">
         <f>-FSM!F235</f>
         <v>0.11455777974233791</v>
       </c>
@@ -14877,7 +14278,7 @@
       <c r="B11" s="51" t="s">
         <v>290</v>
       </c>
-      <c r="C11" s="307">
+      <c r="C11" s="305">
         <f>IF(C32="Observed",(2/3)*C34+(1/3),C35)</f>
         <v>0.36666666666666664</v>
       </c>
@@ -15169,10 +14570,10 @@
       <c r="C40" s="295">
         <v>0.17</v>
       </c>
-      <c r="D40" s="296">
+      <c r="D40" s="295">
         <v>67.97</v>
       </c>
-      <c r="E40" s="297">
+      <c r="E40" s="296">
         <v>1261875720</v>
       </c>
       <c r="F40" s="292">
@@ -15182,10 +14583,10 @@
       <c r="G40" s="186">
         <v>-19380600000</v>
       </c>
-      <c r="H40" s="298">
+      <c r="H40" s="297">
         <v>0.22500000000000001</v>
       </c>
-      <c r="I40" s="299">
+      <c r="I40" s="163">
         <f>C40/(1+(1-H40)*(G40/F40))</f>
         <v>0.20609051417477967</v>
       </c>
@@ -15197,10 +14598,10 @@
       <c r="C41" s="295">
         <v>0.32</v>
       </c>
-      <c r="D41" s="296">
+      <c r="D41" s="295">
         <v>12.28</v>
       </c>
-      <c r="E41" s="297">
+      <c r="E41" s="296">
         <v>1986578999</v>
       </c>
       <c r="F41" s="292">
@@ -15210,10 +14611,10 @@
       <c r="G41" s="291">
         <v>9053000000</v>
       </c>
-      <c r="H41" s="298">
+      <c r="H41" s="297">
         <v>0.22500000000000001</v>
       </c>
-      <c r="I41" s="299">
+      <c r="I41" s="163">
         <f>C41/(1+(1-H41)*(G41/F41))</f>
         <v>0.24852424146876506</v>
       </c>
@@ -15225,10 +14626,10 @@
       <c r="C42" s="295">
         <v>-0.22</v>
       </c>
-      <c r="D42" s="296">
+      <c r="D42" s="295">
         <v>37.54</v>
       </c>
-      <c r="E42" s="297">
+      <c r="E42" s="296">
         <v>109687500</v>
       </c>
       <c r="F42" s="292">
@@ -15238,10 +14639,10 @@
       <c r="G42" s="291">
         <v>-264550000</v>
       </c>
-      <c r="H42" s="298">
+      <c r="H42" s="297">
         <v>0.22500000000000001</v>
       </c>
-      <c r="I42" s="299">
+      <c r="I42" s="163">
         <f>C42/(1+(1-H42)*(G42/F42))</f>
         <v>-0.23152821271046359</v>
       </c>
@@ -15254,10 +14655,10 @@
       <c r="C43" s="295">
         <v>0.05</v>
       </c>
-      <c r="D43" s="296">
+      <c r="D43" s="295">
         <v>36</v>
       </c>
-      <c r="E43" s="297">
+      <c r="E43" s="296">
         <f>DCF!I61</f>
         <v>2868140263</v>
       </c>
@@ -15269,10 +14670,10 @@
         <f>DCF!C65</f>
         <v>-16098949303</v>
       </c>
-      <c r="H43" s="298">
+      <c r="H43" s="297">
         <v>0.22500000000000001</v>
       </c>
-      <c r="I43" s="299"/>
+      <c r="I43" s="163"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" s="286"/>
@@ -15285,7 +14686,7 @@
       <c r="B45" t="s">
         <v>316</v>
       </c>
-      <c r="C45" s="299">
+      <c r="C45" s="163">
         <f>AVERAGE(I40:I41)</f>
         <v>0.22730737782177235</v>
       </c>
@@ -15295,7 +14696,7 @@
         <f>B43&amp;" beta"</f>
         <v>Misr Fertilizers Production Company - Mopco beta</v>
       </c>
-      <c r="C46" s="300">
+      <c r="C46" s="298">
         <f>C45*(1+(1-C7)*(G43/F43))</f>
         <v>0.19984046302149189</v>
       </c>
@@ -15334,49 +14735,47 @@
     <row r="1" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:9" s="51" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="52" t="s">
-        <v>532</v>
+        <v>381</v>
       </c>
       <c r="C2" s="53"/>
       <c r="D2" s="53"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="312" t="s">
-        <v>528</v>
-      </c>
+      <c r="B3" s="310"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="45" t="s">
         <v>317</v>
       </c>
-      <c r="D4" s="313" t="s">
-        <v>531</v>
-      </c>
-      <c r="I4" s="312"/>
+      <c r="D4" s="311" t="s">
+        <v>380</v>
+      </c>
+      <c r="I4" s="310"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="308" t="s">
+      <c r="B6" s="306" t="s">
         <v>318</v>
       </c>
-      <c r="C6" s="309"/>
-      <c r="D6" s="309"/>
-      <c r="E6" s="309"/>
-      <c r="F6" s="309"/>
-      <c r="G6" s="309"/>
+      <c r="C6" s="307"/>
+      <c r="D6" s="307"/>
+      <c r="E6" s="307"/>
+      <c r="F6" s="307"/>
+      <c r="G6" s="307"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="313" t="s">
+      <c r="D7" s="311" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="313" t="s">
+      <c r="E7" s="311" t="s">
         <v>319</v>
       </c>
-      <c r="F7" s="313" t="s">
+      <c r="F7" s="311" t="s">
         <v>320</v>
       </c>
-      <c r="G7" s="313" t="s">
+      <c r="G7" s="311" t="s">
         <v>321</v>
       </c>
     </row>
@@ -15384,16 +14783,16 @@
       <c r="B8" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="D8" s="313" t="s">
+      <c r="D8" s="311" t="s">
         <v>323</v>
       </c>
-      <c r="E8" s="313" t="s">
+      <c r="E8" s="311" t="s">
         <v>324</v>
       </c>
-      <c r="F8" s="313" t="s">
+      <c r="F8" s="311" t="s">
         <v>325</v>
       </c>
-      <c r="G8" s="313" t="s">
+      <c r="G8" s="311" t="s">
         <v>326</v>
       </c>
     </row>
@@ -15401,16 +14800,16 @@
       <c r="B9" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="D9" s="313" t="s">
+      <c r="D9" s="311" t="s">
         <v>328</v>
       </c>
-      <c r="E9" s="313" t="s">
+      <c r="E9" s="311" t="s">
         <v>328</v>
       </c>
-      <c r="F9" s="313" t="s">
+      <c r="F9" s="311" t="s">
         <v>329</v>
       </c>
-      <c r="G9" s="313" t="s">
+      <c r="G9" s="311" t="s">
         <v>330</v>
       </c>
     </row>
@@ -15418,16 +14817,16 @@
       <c r="B10" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="D10" s="313" t="s">
+      <c r="D10" s="311" t="s">
         <v>332</v>
       </c>
-      <c r="E10" s="313" t="s">
+      <c r="E10" s="311" t="s">
         <v>333</v>
       </c>
-      <c r="F10" s="313" t="s">
+      <c r="F10" s="311" t="s">
         <v>332</v>
       </c>
-      <c r="G10" s="313" t="s">
+      <c r="G10" s="311" t="s">
         <v>332</v>
       </c>
     </row>
@@ -15435,65 +14834,63 @@
       <c r="B11" s="35" t="s">
         <v>334</v>
       </c>
-      <c r="D11" s="322">
+      <c r="D11" s="319">
         <f>+DCF!H5</f>
         <v>36</v>
       </c>
-      <c r="E11" s="323">
+      <c r="E11" s="320">
         <v>67.97</v>
       </c>
-      <c r="F11" s="323">
+      <c r="F11" s="320">
         <v>124.1</v>
       </c>
-      <c r="G11" s="323">
+      <c r="G11" s="320">
         <v>0.74</v>
       </c>
-      <c r="I11" s="312" t="s">
-        <v>529</v>
-      </c>
+      <c r="I11" s="310"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="312" t="s">
+      <c r="B12" s="310" t="s">
         <v>335</v>
       </c>
-      <c r="D12" s="324" t="s">
+      <c r="D12" s="321" t="s">
         <v>336</v>
       </c>
-      <c r="E12" s="324" t="s">
+      <c r="E12" s="321" t="s">
         <v>336</v>
       </c>
-      <c r="F12" s="324" t="s">
+      <c r="F12" s="321" t="s">
         <v>336</v>
       </c>
-      <c r="G12" s="324" t="s">
+      <c r="G12" s="321" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="308" t="s">
+      <c r="B14" s="306" t="s">
         <v>337</v>
       </c>
-      <c r="C14" s="309"/>
-      <c r="D14" s="309"/>
-      <c r="E14" s="309"/>
-      <c r="F14" s="309"/>
-      <c r="G14" s="309"/>
+      <c r="C14" s="307"/>
+      <c r="D14" s="307"/>
+      <c r="E14" s="307"/>
+      <c r="F14" s="307"/>
+      <c r="G14" s="307"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="35" t="s">
         <v>338</v>
       </c>
-      <c r="D15" s="325">
+      <c r="D15" s="322">
         <f>+DCF!C72/1000000</f>
         <v>2868.1402629999998</v>
       </c>
-      <c r="E15" s="326">
+      <c r="E15" s="323">
         <v>1263.5999999999999</v>
       </c>
-      <c r="F15" s="326">
+      <c r="F15" s="323">
         <v>476</v>
       </c>
-      <c r="G15" s="326">
+      <c r="G15" s="323">
         <v>8284</v>
       </c>
     </row>
@@ -15501,66 +14898,66 @@
       <c r="B16" s="35" t="s">
         <v>339</v>
       </c>
-      <c r="D16" s="326">
+      <c r="D16" s="323">
         <v>0</v>
       </c>
-      <c r="E16" s="326">
+      <c r="E16" s="323">
         <v>0</v>
       </c>
-      <c r="F16" s="326">
+      <c r="F16" s="323">
         <v>0</v>
       </c>
-      <c r="G16" s="326">
+      <c r="G16" s="323">
         <v>0</v>
       </c>
-      <c r="I16" s="312"/>
+      <c r="I16" s="310"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="45" t="s">
         <v>340</v>
       </c>
-      <c r="D17" s="327">
+      <c r="D17" s="324">
         <f>+D15+D16</f>
         <v>2868.1402629999998</v>
       </c>
-      <c r="E17" s="327">
+      <c r="E17" s="324">
         <f>+E15+E16</f>
         <v>1263.5999999999999</v>
       </c>
-      <c r="F17" s="327">
+      <c r="F17" s="324">
         <f>+F15+F16</f>
         <v>476</v>
       </c>
-      <c r="G17" s="327">
+      <c r="G17" s="324">
         <f>+G15+G16</f>
         <v>8284</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="308" t="s">
+      <c r="B19" s="306" t="s">
         <v>341</v>
       </c>
-      <c r="C19" s="309"/>
-      <c r="D19" s="309"/>
-      <c r="E19" s="309"/>
-      <c r="F19" s="309"/>
-      <c r="G19" s="309"/>
+      <c r="C19" s="307"/>
+      <c r="D19" s="307"/>
+      <c r="E19" s="307"/>
+      <c r="F19" s="307"/>
+      <c r="G19" s="307"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="35" t="s">
         <v>342</v>
       </c>
-      <c r="D20" s="320">
+      <c r="D20" s="317">
         <f>+(FSM!F79+FSM!F88+FSM!F83+FSM!F90)/1000000</f>
         <v>842.05469300000004</v>
       </c>
-      <c r="E20" s="315">
+      <c r="E20" s="312">
         <v>30</v>
       </c>
-      <c r="F20" s="315">
+      <c r="F20" s="312">
         <v>900</v>
       </c>
-      <c r="G20" s="315">
+      <c r="G20" s="312">
         <v>1900</v>
       </c>
     </row>
@@ -15568,16 +14965,16 @@
       <c r="B21" s="35" t="s">
         <v>343</v>
       </c>
-      <c r="D21" s="315">
+      <c r="D21" s="312">
         <v>0</v>
       </c>
-      <c r="E21" s="315">
+      <c r="E21" s="312">
         <v>0</v>
       </c>
-      <c r="F21" s="315">
+      <c r="F21" s="312">
         <v>0</v>
       </c>
-      <c r="G21" s="315">
+      <c r="G21" s="312">
         <v>350</v>
       </c>
     </row>
@@ -15585,17 +14982,17 @@
       <c r="B22" s="35" t="s">
         <v>344</v>
       </c>
-      <c r="D22" s="320">
+      <c r="D22" s="317">
         <f>+D20+D21-(DCF!C65/1000000)</f>
         <v>16941.003995999999</v>
       </c>
-      <c r="E22" s="315">
+      <c r="E22" s="312">
         <v>15000</v>
       </c>
-      <c r="F22" s="315">
+      <c r="F22" s="312">
         <v>4500</v>
       </c>
-      <c r="G22" s="315">
+      <c r="G22" s="312">
         <v>894</v>
       </c>
     </row>
@@ -15603,50 +15000,50 @@
       <c r="B23" s="45" t="s">
         <v>345</v>
       </c>
-      <c r="D23" s="328">
+      <c r="D23" s="325">
         <f>SUM(D20:D21)-SUM(D22)</f>
         <v>-16098.949302999999</v>
       </c>
-      <c r="E23" s="328">
+      <c r="E23" s="325">
         <f t="shared" ref="E23:G23" si="0">SUM(E20:E21)-SUM(E22)</f>
         <v>-14970</v>
       </c>
-      <c r="F23" s="328">
+      <c r="F23" s="325">
         <f t="shared" si="0"/>
         <v>-3600</v>
       </c>
-      <c r="G23" s="328">
+      <c r="G23" s="325">
         <f t="shared" si="0"/>
         <v>1356</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="308" t="s">
+      <c r="B25" s="306" t="s">
         <v>346</v>
       </c>
-      <c r="C25" s="309"/>
-      <c r="D25" s="309"/>
-      <c r="E25" s="309"/>
-      <c r="F25" s="309"/>
-      <c r="G25" s="309"/>
+      <c r="C25" s="307"/>
+      <c r="D25" s="307"/>
+      <c r="E25" s="307"/>
+      <c r="F25" s="307"/>
+      <c r="G25" s="307"/>
     </row>
     <row r="26" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="45" t="s">
         <v>347</v>
       </c>
-      <c r="D26" s="328">
+      <c r="D26" s="325">
         <f>D17*D11</f>
         <v>103253.049468</v>
       </c>
-      <c r="E26" s="328">
+      <c r="E26" s="325">
         <f t="shared" ref="E26:G26" si="1">E17*E11</f>
         <v>85886.891999999993</v>
       </c>
-      <c r="F26" s="328">
+      <c r="F26" s="325">
         <f t="shared" si="1"/>
         <v>59071.6</v>
       </c>
-      <c r="G26" s="328">
+      <c r="G26" s="325">
         <f t="shared" si="1"/>
         <v>6130.16</v>
       </c>
@@ -15655,47 +15052,47 @@
       <c r="B27" s="45" t="s">
         <v>348</v>
       </c>
-      <c r="D27" s="317">
+      <c r="D27" s="314">
         <f>D26+D23</f>
         <v>87154.100164999996</v>
       </c>
-      <c r="E27" s="317">
+      <c r="E27" s="314">
         <f t="shared" ref="E27:G27" si="2">E26+E23</f>
         <v>70916.891999999993</v>
       </c>
-      <c r="F27" s="317">
+      <c r="F27" s="314">
         <f t="shared" si="2"/>
         <v>55471.6</v>
       </c>
-      <c r="G27" s="317">
+      <c r="G27" s="314">
         <f t="shared" si="2"/>
         <v>7486.16</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="308" t="s">
+      <c r="B29" s="306" t="s">
         <v>349</v>
       </c>
-      <c r="C29" s="309"/>
-      <c r="D29" s="309"/>
-      <c r="E29" s="309"/>
-      <c r="F29" s="309"/>
-      <c r="G29" s="309"/>
+      <c r="C29" s="307"/>
+      <c r="D29" s="307"/>
+      <c r="E29" s="307"/>
+      <c r="F29" s="307"/>
+      <c r="G29" s="307"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="312" t="s">
+      <c r="B30" s="310" t="s">
         <v>350</v>
       </c>
-      <c r="D30" s="324" t="s">
+      <c r="D30" s="321" t="s">
         <v>351</v>
       </c>
-      <c r="E30" s="324" t="s">
+      <c r="E30" s="321" t="s">
         <v>352</v>
       </c>
-      <c r="F30" s="324" t="s">
+      <c r="F30" s="321" t="s">
         <v>351</v>
       </c>
-      <c r="G30" s="324" t="s">
+      <c r="G30" s="321" t="s">
         <v>351</v>
       </c>
     </row>
@@ -15703,17 +15100,17 @@
       <c r="B31" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="320">
+      <c r="D31" s="317">
         <f>+FSM!F16/1000000</f>
         <v>26844.075575999999</v>
       </c>
-      <c r="E31" s="315">
+      <c r="E31" s="312">
         <v>22920</v>
       </c>
-      <c r="F31" s="315">
+      <c r="F31" s="312">
         <v>13070</v>
       </c>
-      <c r="G31" s="315">
+      <c r="G31" s="312">
         <v>2820</v>
       </c>
     </row>
@@ -15721,17 +15118,17 @@
       <c r="B32" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="320">
+      <c r="D32" s="317">
         <f>+FSM!F37/1000000</f>
         <v>15279.05955</v>
       </c>
-      <c r="E32" s="315">
+      <c r="E32" s="312">
         <v>10300</v>
       </c>
-      <c r="F32" s="315">
+      <c r="F32" s="312">
         <v>5300</v>
       </c>
-      <c r="G32" s="315">
+      <c r="G32" s="312">
         <v>1020</v>
       </c>
     </row>
@@ -15739,17 +15136,17 @@
       <c r="B33" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="320">
+      <c r="D33" s="317">
         <f>+FSM!F26/1000000</f>
         <v>12960.33052</v>
       </c>
-      <c r="E33" s="315">
+      <c r="E33" s="312">
         <v>9300</v>
       </c>
-      <c r="F33" s="315">
+      <c r="F33" s="312">
         <v>4200</v>
       </c>
-      <c r="G33" s="315">
+      <c r="G33" s="312">
         <v>650</v>
       </c>
     </row>
@@ -15757,77 +15154,77 @@
       <c r="B34" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="D34" s="320">
+      <c r="D34" s="317">
         <f>+FSM!F35/1000000</f>
         <v>11296.540287</v>
       </c>
-      <c r="E34" s="315">
+      <c r="E34" s="312">
         <v>9340</v>
       </c>
-      <c r="F34" s="315">
+      <c r="F34" s="312">
         <v>4320</v>
       </c>
-      <c r="G34" s="315">
+      <c r="G34" s="312">
         <v>325</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="312" t="s">
+      <c r="B35" s="310" t="s">
         <v>353</v>
       </c>
-      <c r="D35" s="329">
+      <c r="D35" s="326">
         <f>+D32/D31</f>
         <v>0.56917808574716855</v>
       </c>
-      <c r="E35" s="329">
+      <c r="E35" s="326">
         <f>+E32/E31</f>
         <v>0.44938917975567189</v>
       </c>
-      <c r="F35" s="329">
+      <c r="F35" s="326">
         <f>+F32/F31</f>
         <v>0.40550879877582252</v>
       </c>
-      <c r="G35" s="329">
+      <c r="G35" s="326">
         <f>+G32/G31</f>
         <v>0.36170212765957449</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="312" t="s">
+      <c r="B36" s="310" t="s">
         <v>354</v>
       </c>
-      <c r="D36" s="324"/>
-      <c r="E36" s="324"/>
-      <c r="F36" s="324"/>
-      <c r="G36" s="324"/>
+      <c r="D36" s="321"/>
+      <c r="E36" s="321"/>
+      <c r="F36" s="321"/>
+      <c r="G36" s="321"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="308" t="s">
+      <c r="B38" s="306" t="s">
         <v>355</v>
       </c>
-      <c r="C38" s="309"/>
-      <c r="D38" s="309"/>
-      <c r="E38" s="309"/>
-      <c r="F38" s="309"/>
-      <c r="G38" s="309"/>
+      <c r="C38" s="307"/>
+      <c r="D38" s="307"/>
+      <c r="E38" s="307"/>
+      <c r="F38" s="307"/>
+      <c r="G38" s="307"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="35" t="s">
         <v>356</v>
       </c>
-      <c r="D39" s="318">
+      <c r="D39" s="315">
         <f>D27/D31</f>
         <v>3.246679138503108</v>
       </c>
-      <c r="E39" s="318">
+      <c r="E39" s="315">
         <f t="shared" ref="E39:G39" si="3">E27/E31</f>
         <v>3.0941052356020937</v>
       </c>
-      <c r="F39" s="318">
+      <c r="F39" s="315">
         <f t="shared" si="3"/>
         <v>4.2441928079571536</v>
       </c>
-      <c r="G39" s="318">
+      <c r="G39" s="315">
         <f t="shared" si="3"/>
         <v>2.6546666666666665</v>
       </c>
@@ -15836,19 +15233,19 @@
       <c r="B40" s="45" t="s">
         <v>357</v>
       </c>
-      <c r="D40" s="319">
+      <c r="D40" s="316">
         <f>D27/D32</f>
         <v>5.7041534447714088</v>
       </c>
-      <c r="E40" s="319">
+      <c r="E40" s="316">
         <f t="shared" ref="E40:G40" si="4">E27/E32</f>
         <v>6.8851351456310672</v>
       </c>
-      <c r="F40" s="319">
+      <c r="F40" s="316">
         <f t="shared" si="4"/>
         <v>10.46633962264151</v>
       </c>
-      <c r="G40" s="319">
+      <c r="G40" s="316">
         <f t="shared" si="4"/>
         <v>7.3393725490196076</v>
       </c>
@@ -15857,19 +15254,19 @@
       <c r="B41" s="35" t="s">
         <v>358</v>
       </c>
-      <c r="D41" s="318">
+      <c r="D41" s="315">
         <f>D27/D33</f>
         <v>6.7246819076493738</v>
       </c>
-      <c r="E41" s="318">
+      <c r="E41" s="315">
         <f t="shared" ref="E41:G41" si="5">E27/E33</f>
         <v>7.6254722580645149</v>
       </c>
-      <c r="F41" s="318">
+      <c r="F41" s="315">
         <f t="shared" si="5"/>
         <v>13.20752380952381</v>
       </c>
-      <c r="G41" s="318">
+      <c r="G41" s="315">
         <f t="shared" si="5"/>
         <v>11.51716923076923</v>
       </c>
@@ -15878,32 +15275,32 @@
       <c r="B42" s="45" t="s">
         <v>359</v>
       </c>
-      <c r="D42" s="319">
+      <c r="D42" s="316">
         <f>D26/D34</f>
         <v>9.1402364657454527</v>
       </c>
-      <c r="E42" s="319">
+      <c r="E42" s="316">
         <f t="shared" ref="E42:G42" si="6">E26/E34</f>
         <v>9.1955987152034258</v>
       </c>
-      <c r="F42" s="319">
+      <c r="F42" s="316">
         <f t="shared" si="6"/>
         <v>13.673981481481482</v>
       </c>
-      <c r="G42" s="319">
+      <c r="G42" s="316">
         <f t="shared" si="6"/>
         <v>18.86203076923077</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="308" t="s">
+      <c r="B44" s="306" t="s">
         <v>360</v>
       </c>
-      <c r="C44" s="309"/>
-      <c r="D44" s="309"/>
-      <c r="E44" s="309"/>
-      <c r="F44" s="309"/>
-      <c r="G44" s="309"/>
+      <c r="C44" s="307"/>
+      <c r="D44" s="307"/>
+      <c r="E44" s="307"/>
+      <c r="F44" s="307"/>
+      <c r="G44" s="307"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D45" s="45" t="s">
@@ -15923,19 +15320,19 @@
       <c r="B46" s="35" t="s">
         <v>365</v>
       </c>
-      <c r="D46" s="318">
+      <c r="D46" s="315">
         <f>AVERAGE($E$39:$G$39)</f>
         <v>3.330988236741971</v>
       </c>
-      <c r="E46" s="318">
+      <c r="E46" s="315">
         <f>AVERAGE($E$40:$G$40)</f>
         <v>8.2302824390973957</v>
       </c>
-      <c r="F46" s="318">
+      <c r="F46" s="315">
         <f>AVERAGE($E$41:$G$41)</f>
         <v>10.78338843278585</v>
       </c>
-      <c r="G46" s="318">
+      <c r="G46" s="315">
         <f>AVERAGE($E$42:$G$42)</f>
         <v>13.91053698863856</v>
       </c>
@@ -15944,19 +15341,19 @@
       <c r="B47" s="45" t="s">
         <v>366</v>
       </c>
-      <c r="D47" s="319">
+      <c r="D47" s="316">
         <f>MEDIAN($E$39:$G$39)</f>
         <v>3.0941052356020937</v>
       </c>
-      <c r="E47" s="319">
+      <c r="E47" s="316">
         <f>MEDIAN($E$40:$G$40)</f>
         <v>7.3393725490196076</v>
       </c>
-      <c r="F47" s="319">
+      <c r="F47" s="316">
         <f>MEDIAN($E$41:$G$41)</f>
         <v>11.51716923076923</v>
       </c>
-      <c r="G47" s="319">
+      <c r="G47" s="316">
         <f>MEDIAN($E$42:$G$42)</f>
         <v>13.673981481481482</v>
       </c>
@@ -15965,19 +15362,19 @@
       <c r="B48" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="D48" s="318">
+      <c r="D48" s="315">
         <f>MAX($E$39:$G$39)</f>
         <v>4.2441928079571536</v>
       </c>
-      <c r="E48" s="318">
+      <c r="E48" s="315">
         <f>MAX($E$40:$G$40)</f>
         <v>10.46633962264151</v>
       </c>
-      <c r="F48" s="318">
+      <c r="F48" s="315">
         <f>MAX($E$41:$G$41)</f>
         <v>13.20752380952381</v>
       </c>
-      <c r="G48" s="318">
+      <c r="G48" s="315">
         <f>MAX($E$42:$G$42)</f>
         <v>18.86203076923077</v>
       </c>
@@ -15986,32 +15383,32 @@
       <c r="B49" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="D49" s="318">
+      <c r="D49" s="315">
         <f>MIN($E$39:$G$39)</f>
         <v>2.6546666666666665</v>
       </c>
-      <c r="E49" s="318">
+      <c r="E49" s="315">
         <f>MIN($E$40:$G$40)</f>
         <v>6.8851351456310672</v>
       </c>
-      <c r="F49" s="318">
+      <c r="F49" s="315">
         <f>MIN($E$41:$G$41)</f>
         <v>7.6254722580645149</v>
       </c>
-      <c r="G49" s="318">
+      <c r="G49" s="315">
         <f>MIN($E$42:$G$42)</f>
         <v>9.1955987152034258</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B51" s="308" t="s">
+      <c r="B51" s="306" t="s">
         <v>367</v>
       </c>
-      <c r="C51" s="309"/>
-      <c r="D51" s="309"/>
-      <c r="E51" s="309"/>
-      <c r="F51" s="309"/>
-      <c r="G51" s="309"/>
+      <c r="C51" s="307"/>
+      <c r="D51" s="307"/>
+      <c r="E51" s="307"/>
+      <c r="F51" s="307"/>
+      <c r="G51" s="307"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B52" s="45" t="s">
@@ -16022,43 +15419,43 @@
       <c r="B53" s="35" t="s">
         <v>369</v>
       </c>
-      <c r="D53" s="318">
+      <c r="D53" s="315">
         <f>E47</f>
         <v>7.3393725490196076</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B54" s="35" t="s">
-        <v>530</v>
-      </c>
-      <c r="D54" s="316">
+        <v>379</v>
+      </c>
+      <c r="D54" s="313">
         <f>D32</f>
         <v>15279.05955</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B55" s="35" t="s">
-        <v>371</v>
-      </c>
-      <c r="D55" s="316">
+        <v>370</v>
+      </c>
+      <c r="D55" s="313">
         <f>D53*D54</f>
         <v>112138.71023610588</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="35" t="s">
-        <v>372</v>
-      </c>
-      <c r="D56" s="316">
+        <v>371</v>
+      </c>
+      <c r="D56" s="313">
         <f>D23</f>
         <v>-16098.949302999999</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B57" s="35" t="s">
-        <v>373</v>
-      </c>
-      <c r="D57" s="316">
+        <v>372</v>
+      </c>
+      <c r="D57" s="313">
         <f>D55-D56</f>
         <v>128237.65953910588</v>
       </c>
@@ -16067,48 +15464,48 @@
       <c r="B58" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="D58" s="316">
+      <c r="D58" s="313">
         <f>$D$17</f>
         <v>2868.1402629999998</v>
       </c>
     </row>
     <row r="59" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B59" s="45" t="s">
-        <v>374</v>
-      </c>
-      <c r="D59" s="321">
+        <v>373</v>
+      </c>
+      <c r="D59" s="318">
         <f>D57/D58</f>
         <v>44.711083761633276</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="45" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B62" s="35" t="s">
-        <v>376</v>
-      </c>
-      <c r="D62" s="318">
+        <v>375</v>
+      </c>
+      <c r="D62" s="315">
         <f>G47</f>
         <v>13.673981481481482</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B63" s="35" t="s">
-        <v>377</v>
-      </c>
-      <c r="D63" s="316">
+        <v>376</v>
+      </c>
+      <c r="D63" s="313">
         <f>D34</f>
         <v>11296.540287</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B64" s="35" t="s">
-        <v>373</v>
-      </c>
-      <c r="D64" s="316">
+        <v>372</v>
+      </c>
+      <c r="D64" s="313">
         <f>D62*D63</f>
         <v>154468.68268924751</v>
       </c>
@@ -16117,37 +15514,37 @@
       <c r="B65" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="D65" s="316">
+      <c r="D65" s="313">
         <f>$D$17</f>
         <v>2868.1402629999998</v>
       </c>
     </row>
     <row r="66" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B66" s="45" t="s">
-        <v>374</v>
-      </c>
-      <c r="D66" s="321">
+        <v>373</v>
+      </c>
+      <c r="D66" s="318">
         <f>D64/D65</f>
         <v>53.856739393797042</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="45" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="35" t="s">
-        <v>379</v>
-      </c>
-      <c r="D69" s="318">
+        <v>378</v>
+      </c>
+      <c r="D69" s="315">
         <f>E40</f>
         <v>6.8851351456310672</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" s="35" t="s">
-        <v>530</v>
+        <v>379</v>
       </c>
       <c r="D70" s="19">
         <f>D32</f>
@@ -16156,7 +15553,7 @@
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" s="35" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D71" s="19">
         <f>D69*D70</f>
@@ -16165,7 +15562,7 @@
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" s="35" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D72" s="19">
         <f>D23</f>
@@ -16174,7 +15571,7 @@
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="35" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D73" s="19">
         <f>D71-D72</f>
@@ -16185,3302 +15582,17 @@
       <c r="B74" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="D74" s="316">
+      <c r="D74" s="313">
         <f>$D$17</f>
         <v>2868.1402629999998</v>
       </c>
     </row>
     <row r="75" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B75" s="45" t="s">
-        <v>374</v>
-      </c>
-      <c r="D75" s="321">
+        <v>373</v>
+      </c>
+      <c r="D75" s="318">
         <f>D73/D74</f>
-        <v>42.291285669558278</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B1:I42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="2" style="6" customWidth="1"/>
-    <col min="2" max="2" width="40" style="6" customWidth="1"/>
-    <col min="3" max="3" width="2" style="6" customWidth="1"/>
-    <col min="4" max="7" width="17" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2" style="6" customWidth="1"/>
-    <col min="9" max="9" width="48" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:9" s="51" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="52" t="s">
-        <v>533</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="312" t="s">
-        <v>527</v>
-      </c>
-      <c r="I3" s="312"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="308" t="s">
-        <v>380</v>
-      </c>
-      <c r="C5" s="309"/>
-      <c r="D5" s="309"/>
-      <c r="E5" s="309"/>
-      <c r="F5" s="309"/>
-      <c r="G5" s="309"/>
-      <c r="H5" s="35"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="35" t="s">
-        <v>381</v>
-      </c>
-      <c r="D6" s="313" t="s">
-        <v>382</v>
-      </c>
-      <c r="E6" s="313" t="s">
-        <v>383</v>
-      </c>
-      <c r="F6" s="313" t="s">
-        <v>384</v>
-      </c>
-      <c r="G6" s="313" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="35" t="s">
-        <v>386</v>
-      </c>
-      <c r="D7" s="313" t="s">
-        <v>387</v>
-      </c>
-      <c r="E7" s="313" t="s">
-        <v>388</v>
-      </c>
-      <c r="F7" s="313" t="s">
-        <v>389</v>
-      </c>
-      <c r="G7" s="313" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="35" t="s">
-        <v>391</v>
-      </c>
-      <c r="D8" s="313" t="s">
-        <v>392</v>
-      </c>
-      <c r="E8" s="313" t="s">
-        <v>392</v>
-      </c>
-      <c r="F8" s="313" t="s">
-        <v>392</v>
-      </c>
-      <c r="G8" s="313" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="35" t="s">
-        <v>394</v>
-      </c>
-      <c r="D9" s="313" t="s">
-        <v>395</v>
-      </c>
-      <c r="E9" s="313" t="s">
-        <v>396</v>
-      </c>
-      <c r="F9" s="313" t="s">
-        <v>397</v>
-      </c>
-      <c r="G9" s="313" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="35" t="s">
-        <v>399</v>
-      </c>
-      <c r="D10" s="313" t="s">
-        <v>400</v>
-      </c>
-      <c r="E10" s="313" t="s">
-        <v>400</v>
-      </c>
-      <c r="F10" s="313" t="s">
-        <v>400</v>
-      </c>
-      <c r="G10" s="313" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="35" t="s">
-        <v>401</v>
-      </c>
-      <c r="D11" s="314">
-        <v>0.50800000000000001</v>
-      </c>
-      <c r="E11" s="314">
-        <v>1</v>
-      </c>
-      <c r="F11" s="314">
-        <v>1</v>
-      </c>
-      <c r="G11" s="314">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="35" t="s">
-        <v>402</v>
-      </c>
-      <c r="D12" s="313" t="s">
-        <v>403</v>
-      </c>
-      <c r="E12" s="313" t="s">
-        <v>404</v>
-      </c>
-      <c r="F12" s="313" t="s">
-        <v>404</v>
-      </c>
-      <c r="G12" s="313" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="308" t="s">
-        <v>406</v>
-      </c>
-      <c r="C14" s="309"/>
-      <c r="D14" s="309"/>
-      <c r="E14" s="309"/>
-      <c r="F14" s="309"/>
-      <c r="G14" s="309"/>
-      <c r="H14" s="35"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="35" t="s">
-        <v>407</v>
-      </c>
-      <c r="D15" s="315">
-        <v>3620</v>
-      </c>
-      <c r="E15" s="315">
-        <v>3600</v>
-      </c>
-      <c r="F15" s="315">
-        <v>2350</v>
-      </c>
-      <c r="G15" s="315"/>
-      <c r="I15" s="312"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="35" t="s">
-        <v>408</v>
-      </c>
-      <c r="D16" s="316">
-        <f>IFERROR(D15/D11,"NM")</f>
-        <v>7125.9842519685035</v>
-      </c>
-      <c r="E16" s="316">
-        <f>IFERROR(E15/E11,"NM")</f>
-        <v>3600</v>
-      </c>
-      <c r="F16" s="316">
-        <f>IFERROR(F15/F11,"NM")</f>
-        <v>2350</v>
-      </c>
-      <c r="G16" s="316">
-        <f>IFERROR(G15/G11,"NM")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="35" t="s">
-        <v>409</v>
-      </c>
-      <c r="D17" s="315">
-        <v>1040</v>
-      </c>
-      <c r="E17" s="315">
-        <v>0</v>
-      </c>
-      <c r="F17" s="315">
-        <v>0</v>
-      </c>
-      <c r="G17" s="315"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="D18" s="317">
-        <f>IFERROR(D16+D17,"NM")</f>
-        <v>8165.9842519685035</v>
-      </c>
-      <c r="E18" s="317">
-        <f>IFERROR(E16+E17,"NM")</f>
-        <v>3600</v>
-      </c>
-      <c r="F18" s="317">
-        <f>IFERROR(F16+F17,"NM")</f>
-        <v>2350</v>
-      </c>
-      <c r="G18" s="317">
-        <f>IFERROR(G16+G17,"NM")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="308" t="s">
-        <v>411</v>
-      </c>
-      <c r="C20" s="309"/>
-      <c r="D20" s="309"/>
-      <c r="E20" s="309"/>
-      <c r="F20" s="309"/>
-      <c r="G20" s="309"/>
-      <c r="H20" s="35"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="35" t="s">
-        <v>412</v>
-      </c>
-      <c r="D21" s="315">
-        <v>2000</v>
-      </c>
-      <c r="E21" s="315">
-        <v>800</v>
-      </c>
-      <c r="F21" s="313" t="s">
-        <v>413</v>
-      </c>
-      <c r="G21" s="315"/>
-      <c r="I21" s="312"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="35" t="s">
-        <v>414</v>
-      </c>
-      <c r="D22" s="315">
-        <v>650</v>
-      </c>
-      <c r="E22" s="315">
-        <v>450</v>
-      </c>
-      <c r="F22" s="313" t="s">
-        <v>413</v>
-      </c>
-      <c r="G22" s="315"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="308" t="s">
-        <v>415</v>
-      </c>
-      <c r="C24" s="309"/>
-      <c r="D24" s="309"/>
-      <c r="E24" s="309"/>
-      <c r="F24" s="309"/>
-      <c r="G24" s="309"/>
-      <c r="H24" s="35"/>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="35" t="s">
-        <v>416</v>
-      </c>
-      <c r="D25" s="318">
-        <f>IFERROR(D18/D21,"NM")</f>
-        <v>4.0829921259842514</v>
-      </c>
-      <c r="E25" s="318">
-        <f>IFERROR(E18/E21,"NM")</f>
-        <v>4.5</v>
-      </c>
-      <c r="F25" s="318" t="str">
-        <f>IFERROR(F18/F21,"NM")</f>
-        <v>NM</v>
-      </c>
-      <c r="G25" s="318" t="str">
-        <f>IFERROR(G18/G21,"NM")</f>
-        <v>NM</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="45" t="s">
-        <v>417</v>
-      </c>
-      <c r="D26" s="319">
-        <f>IFERROR(D18/D22,"NM")</f>
-        <v>12.563052695336159</v>
-      </c>
-      <c r="E26" s="319">
-        <f>IFERROR(E18/E22,"NM")</f>
-        <v>8</v>
-      </c>
-      <c r="F26" s="319" t="str">
-        <f>IFERROR(F18/F22,"NM")</f>
-        <v>NM</v>
-      </c>
-      <c r="G26" s="319" t="str">
-        <f>IFERROR(G18/G22,"NM")</f>
-        <v>NM</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="308" t="s">
-        <v>418</v>
-      </c>
-      <c r="C28" s="309"/>
-      <c r="D28" s="309"/>
-      <c r="E28" s="309"/>
-      <c r="F28" s="309"/>
-      <c r="G28" s="309"/>
-      <c r="H28" s="35"/>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D29" s="45" t="s">
-        <v>419</v>
-      </c>
-      <c r="E29" s="45" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="35" t="s">
-        <v>365</v>
-      </c>
-      <c r="D30" s="318">
-        <f>IFERROR(AVERAGE(D25:G25),"NM")</f>
-        <v>4.2914960629921257</v>
-      </c>
-      <c r="E30" s="318">
-        <f>IFERROR(AVERAGE(D26:G26),"NM")</f>
-        <v>10.28152634766808</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="45" t="s">
-        <v>366</v>
-      </c>
-      <c r="D31" s="319">
-        <f>IFERROR(MEDIAN(D25:G25),"NM")</f>
-        <v>4.2914960629921257</v>
-      </c>
-      <c r="E31" s="319">
-        <f>IFERROR(MEDIAN(D26:G26),"NM")</f>
-        <v>10.28152634766808</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" s="318">
-        <f>IFERROR(MAX(D25:G25),"NM")</f>
-        <v>4.5</v>
-      </c>
-      <c r="E32" s="318">
-        <f>IFERROR(MAX(D26:G26),"NM")</f>
-        <v>12.563052695336159</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D33" s="318">
-        <f>IFERROR(MIN(D25:G25),"NM")</f>
-        <v>4.0829921259842514</v>
-      </c>
-      <c r="E33" s="318">
-        <f>IFERROR(MIN(D26:G26),"NM")</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="308" t="s">
-        <v>421</v>
-      </c>
-      <c r="C35" s="309"/>
-      <c r="D35" s="309"/>
-      <c r="E35" s="309"/>
-      <c r="F35" s="309"/>
-      <c r="G35" s="309"/>
-      <c r="H35" s="35"/>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="35" t="s">
-        <v>422</v>
-      </c>
-      <c r="D36" s="318">
-        <f>+E31</f>
-        <v>10.28152634766808</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="35" t="s">
-        <v>423</v>
-      </c>
-      <c r="D37" s="320">
-        <f>+FSM!F37/1000000</f>
-        <v>15279.05955</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="35" t="s">
-        <v>424</v>
-      </c>
-      <c r="D38" s="316">
-        <f>+D36*D37</f>
-        <v>157092.05333091461</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="35" t="s">
-        <v>425</v>
-      </c>
-      <c r="D39" s="320">
-        <f>-DCF!C65/1000000</f>
-        <v>16098.949302999999</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="35" t="s">
-        <v>373</v>
-      </c>
-      <c r="D40" s="316">
-        <f>+D38+D39</f>
-        <v>173191.00263391461</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="45" t="s">
-        <v>374</v>
-      </c>
-      <c r="D41" s="321">
-        <f>+D40/(DCF!C72/1000000)</f>
-        <v>60.38442570893006</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="346"/>
-      <c r="C42" s="347"/>
-      <c r="D42" s="347"/>
-      <c r="E42" s="347"/>
-      <c r="F42" s="347"/>
-      <c r="G42" s="347"/>
-      <c r="H42" s="347"/>
-      <c r="I42" s="347"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B42:I42"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="B1:U86"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="2" style="6" customWidth="1"/>
-    <col min="2" max="2" width="46" style="6" customWidth="1"/>
-    <col min="3" max="4" width="15" style="6" customWidth="1"/>
-    <col min="5" max="5" width="3" style="6" customWidth="1"/>
-    <col min="6" max="6" width="44" style="6" customWidth="1"/>
-    <col min="7" max="8" width="15" style="6" customWidth="1"/>
-    <col min="9" max="9" width="3" style="6" customWidth="1"/>
-    <col min="10" max="10" width="52" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="52" t="s">
-        <v>426</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="312" t="s">
-        <v>427</v>
-      </c>
-      <c r="J3" s="312" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="308" t="s">
-        <v>429</v>
-      </c>
-      <c r="C5" s="309"/>
-      <c r="D5" s="309"/>
-      <c r="F5" s="308" t="s">
-        <v>430</v>
-      </c>
-      <c r="G5" s="309"/>
-      <c r="H5" s="309"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="45" t="s">
-        <v>431</v>
-      </c>
-      <c r="F6" s="45" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="35" t="s">
-        <v>433</v>
-      </c>
-      <c r="C7" s="330">
-        <f>+DCF!H5</f>
-        <v>36</v>
-      </c>
-      <c r="F7" s="35" t="s">
-        <v>434</v>
-      </c>
-      <c r="G7" s="316">
-        <f>+C26*C25*C19</f>
-        <v>26839.653750000001</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="35" t="s">
-        <v>435</v>
-      </c>
-      <c r="C8" s="320">
-        <f>+DCF!C72/1000000</f>
-        <v>2868.1402629999998</v>
-      </c>
-      <c r="F8" s="35" t="s">
-        <v>436</v>
-      </c>
-      <c r="G8" s="316">
-        <f>+C27*C25*C19</f>
-        <v>26839.653750000001</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="35" t="s">
-        <v>437</v>
-      </c>
-      <c r="C9" s="320">
-        <f>+FSM!G35/1000000</f>
-        <v>11615.299123329996</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>438</v>
-      </c>
-      <c r="G9" s="316">
-        <f>+C24*C19</f>
-        <v>53679.307500000003</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="35" t="s">
-        <v>439</v>
-      </c>
-      <c r="C10" s="331">
-        <f>+C9/C8</f>
-        <v>4.0497667680940737</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>440</v>
-      </c>
-      <c r="G10" s="316">
-        <f>+C31*C19+C32*G7</f>
-        <v>1341.9826875000001</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="35" t="s">
-        <v>441</v>
-      </c>
-      <c r="C11" s="332">
-        <f>+FSM!G46</f>
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="F11" s="45" t="s">
-        <v>442</v>
-      </c>
-      <c r="G11" s="328">
-        <f>SUM(G7:G10)</f>
-        <v>108700.59768750001</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="35" t="s">
-        <v>443</v>
-      </c>
-      <c r="C12" s="320">
-        <f>+'Trading Comps'!D22</f>
-        <v>16941.003995999999</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F13" s="35" t="s">
-        <v>445</v>
-      </c>
-      <c r="G13" s="316">
-        <f>+C25*C19</f>
-        <v>53679.307500000003</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="45" t="s">
-        <v>446</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="G14" s="316">
-        <f>+C24*C19</f>
-        <v>53679.307500000003</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="35" t="s">
-        <v>448</v>
-      </c>
-      <c r="C15" s="330">
-        <f>+'Trading Comps'!E11</f>
-        <v>67.97</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>449</v>
-      </c>
-      <c r="G15" s="316">
-        <f>+C31*C19</f>
-        <v>1073.5861500000001</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="35" t="s">
-        <v>450</v>
-      </c>
-      <c r="C16" s="314">
-        <v>0.25</v>
-      </c>
-      <c r="F16" s="35" t="s">
-        <v>451</v>
-      </c>
-      <c r="G16" s="316">
-        <f>+C32*G7</f>
-        <v>268.39653750000002</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="35" t="s">
-        <v>452</v>
-      </c>
-      <c r="C17" s="331">
-        <f>+C15*(1+C16)</f>
-        <v>84.962500000000006</v>
-      </c>
-      <c r="F17" s="45" t="s">
-        <v>453</v>
-      </c>
-      <c r="G17" s="328">
-        <f>SUM(G13:G16)</f>
-        <v>108700.59768750001</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="35" t="s">
-        <v>454</v>
-      </c>
-      <c r="C18" s="320">
-        <f>+'Trading Comps'!E17</f>
-        <v>1263.5999999999999</v>
-      </c>
-      <c r="F18" s="45" t="s">
-        <v>455</v>
-      </c>
-      <c r="G18" s="333" t="str">
-        <f>IF(ROUND(G11-G17,2)=0,"Yes","NO — CHECK")</f>
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="45" t="s">
-        <v>456</v>
-      </c>
-      <c r="C19" s="328">
-        <f>+C17*C18</f>
-        <v>107358.61500000001</v>
-      </c>
-      <c r="F19" s="35" t="s">
-        <v>457</v>
-      </c>
-      <c r="G19" s="329">
-        <f>+G8/C12</f>
-        <v>1.5843012466284292</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="35" t="s">
-        <v>458</v>
-      </c>
-      <c r="C20" s="334">
-        <f>+'Trading Comps'!E34</f>
-        <v>9340</v>
-      </c>
-      <c r="J20" s="312" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="35" t="s">
-        <v>460</v>
-      </c>
-      <c r="C21" s="335">
-        <f>+C19/C20</f>
-        <v>11.494498394004284</v>
-      </c>
-      <c r="F21" s="308" t="s">
-        <v>461</v>
-      </c>
-      <c r="G21" s="309"/>
-      <c r="H21" s="309"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F22" s="35" t="s">
-        <v>462</v>
-      </c>
-      <c r="G22" s="336">
-        <v>32600</v>
-      </c>
-      <c r="J22" s="312" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="45" t="s">
-        <v>464</v>
-      </c>
-      <c r="F23" s="35" t="s">
-        <v>465</v>
-      </c>
-      <c r="G23" s="314">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="35" t="s">
-        <v>466</v>
-      </c>
-      <c r="C24" s="314">
-        <v>0.5</v>
-      </c>
-      <c r="F24" s="35" t="s">
-        <v>467</v>
-      </c>
-      <c r="G24" s="336">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="35" t="s">
-        <v>468</v>
-      </c>
-      <c r="C25" s="337">
-        <f>1-C24</f>
-        <v>0.5</v>
-      </c>
-      <c r="F25" s="35" t="s">
-        <v>469</v>
-      </c>
-      <c r="G25" s="316">
-        <f>+G23*G24</f>
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="35" t="s">
-        <v>470</v>
-      </c>
-      <c r="C26" s="314">
-        <v>0.5</v>
-      </c>
-      <c r="F26" s="35" t="s">
-        <v>471</v>
-      </c>
-      <c r="G26" s="338">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="C27" s="337">
-        <f>1-C26</f>
-        <v>0.5</v>
-      </c>
-      <c r="F27" s="35" t="s">
-        <v>473</v>
-      </c>
-      <c r="G27" s="316">
-        <f>+G25/G26</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="C28" s="339">
-        <v>0.24</v>
-      </c>
-      <c r="F28" s="35" t="s">
-        <v>475</v>
-      </c>
-      <c r="G28" s="316">
-        <f>+G25*C11</f>
-        <v>540</v>
-      </c>
-      <c r="J28" s="312" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="C29" s="332">
-        <f>+FSM!G240</f>
-        <v>0.12879356804692393</v>
-      </c>
-      <c r="F29" s="45" t="s">
-        <v>478</v>
-      </c>
-      <c r="J29" s="312" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="35" t="s">
-        <v>480</v>
-      </c>
-      <c r="C30" s="336">
-        <v>500</v>
-      </c>
-      <c r="F30" s="45" t="s">
-        <v>481</v>
-      </c>
-      <c r="G30" s="328">
-        <f>+C19-(G22+G25-G28)</f>
-        <v>72898.615000000005</v>
-      </c>
-      <c r="J30" s="312" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="35" t="s">
-        <v>483</v>
-      </c>
-      <c r="C31" s="314">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="35" t="s">
-        <v>484</v>
-      </c>
-      <c r="C32" s="314">
-        <v>0.01</v>
-      </c>
-      <c r="F32" s="308" t="s">
-        <v>485</v>
-      </c>
-      <c r="G32" s="309"/>
-      <c r="H32" s="309"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F33" s="35" t="s">
-        <v>486</v>
-      </c>
-      <c r="G33" s="316">
-        <f>+C9</f>
-        <v>11615.299123329996</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="45" t="s">
-        <v>487</v>
-      </c>
-      <c r="F34" s="35" t="s">
-        <v>488</v>
-      </c>
-      <c r="G34" s="316">
-        <f>+C20</f>
-        <v>9340</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="35" t="s">
-        <v>489</v>
-      </c>
-      <c r="C35" s="316">
-        <f>+C24*C19/C7</f>
-        <v>1491.0918750000001</v>
-      </c>
-      <c r="F35" s="45" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="35" t="s">
-        <v>491</v>
-      </c>
-      <c r="C36" s="335">
-        <f>+C17/C7</f>
-        <v>2.3600694444444446</v>
-      </c>
-      <c r="F36" s="35" t="s">
-        <v>492</v>
-      </c>
-      <c r="G36" s="316">
-        <f>-C28*G7</f>
-        <v>-6441.5168999999996</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="35" t="s">
-        <v>493</v>
-      </c>
-      <c r="C37" s="335">
-        <f>+C24*C17/C7</f>
-        <v>1.1800347222222223</v>
-      </c>
-      <c r="F37" s="35" t="s">
-        <v>494</v>
-      </c>
-      <c r="G37" s="316">
-        <f>-C29*(G8+G10)</f>
-        <v>-3629.6135101868276</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F38" s="35" t="s">
-        <v>495</v>
-      </c>
-      <c r="G38" s="316">
-        <f>+C30</f>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F39" s="35" t="s">
-        <v>496</v>
-      </c>
-      <c r="G39" s="316">
-        <f>-G27</f>
-        <v>-120</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F40" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="G40" s="316">
-        <f>-G16/5</f>
-        <v>-53.679307500000007</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F41" s="35" t="s">
-        <v>498</v>
-      </c>
-      <c r="G41" s="316">
-        <f>-SUM(G36:G40)*C11</f>
-        <v>2192.5821864795362</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F42" s="35" t="s">
-        <v>499</v>
-      </c>
-      <c r="G42" s="316">
-        <f>SUM(G36:G41)</f>
-        <v>-7552.2275312072907</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F43" s="45" t="s">
-        <v>500</v>
-      </c>
-      <c r="G43" s="328">
-        <f>+G33+G34+G42</f>
-        <v>13403.071592122707</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F44" s="35" t="s">
-        <v>501</v>
-      </c>
-      <c r="G44" s="316">
-        <f>+C8+C35</f>
-        <v>4359.2321379999994</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F45" s="45" t="s">
-        <v>502</v>
-      </c>
-      <c r="G45" s="340">
-        <f>+G43/G44</f>
-        <v>3.074640479750177</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F46" s="35" t="s">
-        <v>503</v>
-      </c>
-      <c r="G46" s="331">
-        <f>+C10</f>
-        <v>4.0497667680940737</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F47" s="45" t="s">
-        <v>504</v>
-      </c>
-      <c r="G47" s="340">
-        <f>+G45-G46</f>
-        <v>-0.9751262883438967</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F48" s="45" t="s">
-        <v>505</v>
-      </c>
-      <c r="G48" s="341">
-        <f>+G47/G46</f>
-        <v>-0.24078578944999757</v>
-      </c>
-    </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="F49" s="35" t="s">
-        <v>506</v>
-      </c>
-      <c r="G49" s="316">
-        <f>MAX(0,-G47*G44/(1-C11))</f>
-        <v>5484.905619041765</v>
-      </c>
-    </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="F51" s="308" t="s">
-        <v>507</v>
-      </c>
-      <c r="G51" s="309"/>
-      <c r="H51" s="309"/>
-    </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="F52" s="35"/>
-      <c r="G52" s="45" t="s">
-        <v>508</v>
-      </c>
-      <c r="H52" s="45" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="F53" s="35" t="s">
-        <v>510</v>
-      </c>
-      <c r="G53" s="337">
-        <f>+'Trading Comps'!D31/('Trading Comps'!D31+'Trading Comps'!E31)</f>
-        <v>0.53942679061733123</v>
-      </c>
-      <c r="H53" s="337">
-        <f>1-G53</f>
-        <v>0.46057320938266877</v>
-      </c>
-    </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="F54" s="35" t="s">
-        <v>511</v>
-      </c>
-      <c r="G54" s="337">
-        <f>+'Trading Comps'!D32/('Trading Comps'!D32+'Trading Comps'!E32)</f>
-        <v>0.59732686888404385</v>
-      </c>
-      <c r="H54" s="337">
-        <f>1-G54</f>
-        <v>0.40267313111595615</v>
-      </c>
-    </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="F55" s="35" t="s">
-        <v>512</v>
-      </c>
-      <c r="G55" s="337">
-        <f>+'Trading Comps'!D34/('Trading Comps'!D34+'Trading Comps'!E34)</f>
-        <v>0.54740475534633404</v>
-      </c>
-      <c r="H55" s="337">
-        <f>1-G55</f>
-        <v>0.45259524465366596</v>
-      </c>
-    </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="F56" s="35" t="s">
-        <v>513</v>
-      </c>
-      <c r="G56" s="337">
-        <f>+C8/G44</f>
-        <v>0.65794620983774743</v>
-      </c>
-      <c r="H56" s="337">
-        <f>+C35/G44</f>
-        <v>0.34205379016225274</v>
-      </c>
-    </row>
-    <row r="57" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="F57" s="346" t="s">
-        <v>514</v>
-      </c>
-      <c r="G57" s="347"/>
-      <c r="H57" s="347"/>
-      <c r="I57" s="347"/>
-      <c r="J57" s="347"/>
-    </row>
-    <row r="60" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B60" s="308" t="s">
-        <v>515</v>
-      </c>
-      <c r="C60" s="309"/>
-      <c r="D60" s="309"/>
-      <c r="E60" s="309"/>
-      <c r="F60" s="309"/>
-      <c r="G60" s="309"/>
-    </row>
-    <row r="61" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B61" s="45" t="s">
-        <v>516</v>
-      </c>
-      <c r="C61" s="342">
-        <v>0.1</v>
-      </c>
-      <c r="D61" s="342">
-        <v>0.2</v>
-      </c>
-      <c r="E61" s="342">
-        <v>0.25</v>
-      </c>
-      <c r="F61" s="342">
-        <v>0.3</v>
-      </c>
-      <c r="G61" s="342">
-        <v>0.4</v>
-      </c>
-      <c r="L61" s="45" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="62" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B62" s="342">
-        <v>0</v>
-      </c>
-      <c r="C62" s="343">
-        <f>+U62</f>
-        <v>-0.35138480686714291</v>
-      </c>
-      <c r="D62" s="343">
-        <f>+U63</f>
-        <v>-0.45873491385277354</v>
-      </c>
-      <c r="E62" s="343">
-        <f>+U64</f>
-        <v>-0.51240996734558975</v>
-      </c>
-      <c r="F62" s="343">
-        <f>+U65</f>
-        <v>-0.56608502083840517</v>
-      </c>
-      <c r="G62" s="343">
-        <f>+U66</f>
-        <v>-0.67343512782403614</v>
-      </c>
-      <c r="L62" s="329">
-        <f>$B62</f>
-        <v>0</v>
-      </c>
-      <c r="M62" s="329">
-        <f>C$61</f>
-        <v>0.1</v>
-      </c>
-      <c r="N62" s="344">
-        <f>C15*(1+M62)*C18</f>
-        <v>94475.581200000001</v>
-      </c>
-      <c r="O62" s="344">
-        <f>C26*(1-L62)*N62</f>
-        <v>47237.7906</v>
-      </c>
-      <c r="P62" s="344">
-        <f>(1-C26)*(1-L62)*N62</f>
-        <v>47237.7906</v>
-      </c>
-      <c r="Q62" s="344">
-        <f>C31*N62+C32*O62</f>
-        <v>1417.133718</v>
-      </c>
-      <c r="R62" s="344">
-        <f>(-C28*O62-C29*(P62+Q62)+C30-G27-C32*O62/5)*(1-C11)</f>
-        <v>-13421.439639155407</v>
-      </c>
-      <c r="S62" s="344">
-        <f>C9+C20+R62</f>
-        <v>7533.8594841745908</v>
-      </c>
-      <c r="T62" s="344">
-        <f>C8+L62*N62/C7</f>
-        <v>2868.1402629999998</v>
-      </c>
-      <c r="U62" s="345">
-        <f>S62/T62/C10-1</f>
-        <v>-0.35138480686714291</v>
-      </c>
-    </row>
-    <row r="63" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B63" s="342">
-        <v>0.25</v>
-      </c>
-      <c r="C63" s="343">
-        <f>+U67</f>
-        <v>-0.23352992966901631</v>
-      </c>
-      <c r="D63" s="343">
-        <f>+U68</f>
-        <v>-0.31086703077303035</v>
-      </c>
-      <c r="E63" s="343">
-        <f>+U69</f>
-        <v>-0.3485782481475499</v>
-      </c>
-      <c r="F63" s="343">
-        <f>+U70</f>
-        <v>-0.38567213860266036</v>
-      </c>
-      <c r="G63" s="343">
-        <f>+U71</f>
-        <v>-0.45806759547250531</v>
-      </c>
-      <c r="L63" s="329">
-        <f>$B62</f>
-        <v>0</v>
-      </c>
-      <c r="M63" s="329">
-        <f>D$61</f>
-        <v>0.2</v>
-      </c>
-      <c r="N63" s="344">
-        <f>C15*(1+M63)*C18</f>
-        <v>103064.27039999998</v>
-      </c>
-      <c r="O63" s="344">
-        <f>C26*(1-L63)*N63</f>
-        <v>51532.13519999999</v>
-      </c>
-      <c r="P63" s="344">
-        <f>(1-C26)*(1-L63)*N63</f>
-        <v>51532.13519999999</v>
-      </c>
-      <c r="Q63" s="344">
-        <f>C31*N63+C32*O63</f>
-        <v>1545.9640559999998</v>
-      </c>
-      <c r="R63" s="344">
-        <f>(-C28*O63-C29*(P63+Q63)+C30-G27-C32*O63/5)*(1-C11)</f>
-        <v>-14668.343242714984</v>
-      </c>
-      <c r="S63" s="344">
-        <f>C9+C20+R63</f>
-        <v>6286.9558806150144</v>
-      </c>
-      <c r="T63" s="344">
-        <f>C8+L63*N63/C7</f>
-        <v>2868.1402629999998</v>
-      </c>
-      <c r="U63" s="345">
-        <f>S63/T63/C10-1</f>
-        <v>-0.45873491385277354</v>
-      </c>
-    </row>
-    <row r="64" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B64" s="342">
-        <v>0.5</v>
-      </c>
-      <c r="C64" s="343">
-        <f>+U72</f>
-        <v>-0.15266869279981787</v>
-      </c>
-      <c r="D64" s="343">
-        <f>+U73</f>
-        <v>-0.21222832785640933</v>
-      </c>
-      <c r="E64" s="343">
-        <f>+U74</f>
-        <v>-0.24078578944999751</v>
-      </c>
-      <c r="F64" s="343">
-        <f>+U75</f>
-        <v>-0.26857234367700999</v>
-      </c>
-      <c r="G64" s="343">
-        <f>+U76</f>
-        <v>-0.32195431159664711</v>
-      </c>
-      <c r="L64" s="329">
-        <f>$B62</f>
-        <v>0</v>
-      </c>
-      <c r="M64" s="329">
-        <f>E$61</f>
-        <v>0.25</v>
-      </c>
-      <c r="N64" s="344">
-        <f>C15*(1+M64)*C18</f>
-        <v>107358.61500000001</v>
-      </c>
-      <c r="O64" s="344">
-        <f>C26*(1-L64)*N64</f>
-        <v>53679.307500000003</v>
-      </c>
-      <c r="P64" s="344">
-        <f>(1-C26)*(1-L64)*N64</f>
-        <v>53679.307500000003</v>
-      </c>
-      <c r="Q64" s="344">
-        <f>C31*N64+C32*O64</f>
-        <v>1610.3792250000001</v>
-      </c>
-      <c r="R64" s="344">
-        <f>(-C28*O64-C29*(P64+Q64)+C30-G27-C32*O64/5)*(1-C11)</f>
-        <v>-15291.795044494782</v>
-      </c>
-      <c r="S64" s="344">
-        <f>C9+C20+R64</f>
-        <v>5663.5040788352162</v>
-      </c>
-      <c r="T64" s="344">
-        <f>C8+L64*N64/C7</f>
-        <v>2868.1402629999998</v>
-      </c>
-      <c r="U64" s="345">
-        <f>S64/T64/C10-1</f>
-        <v>-0.51240996734558975</v>
-      </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B65" s="342">
-        <v>0.75</v>
-      </c>
-      <c r="C65" s="343">
-        <f>+U77</f>
-        <v>-9.3745954468974269E-2</v>
-      </c>
-      <c r="D65" s="343">
-        <f>+U78</f>
-        <v>-0.1417426447100798</v>
-      </c>
-      <c r="E65" s="343">
-        <f>+U79</f>
-        <v>-0.16447921651927211</v>
-      </c>
-      <c r="F65" s="343">
-        <f>+U80</f>
-        <v>-0.18643256012018261</v>
-      </c>
-      <c r="G65" s="343">
-        <f>+U81</f>
-        <v>-0.22814605546303257</v>
-      </c>
-      <c r="L65" s="329">
-        <f>$B62</f>
-        <v>0</v>
-      </c>
-      <c r="M65" s="329">
-        <f>F$61</f>
-        <v>0.3</v>
-      </c>
-      <c r="N65" s="344">
-        <f>C15*(1+M65)*C18</f>
-        <v>111652.9596</v>
-      </c>
-      <c r="O65" s="344">
-        <f>C26*(1-L65)*N65</f>
-        <v>55826.479800000001</v>
-      </c>
-      <c r="P65" s="344">
-        <f>(1-C26)*(1-L65)*N65</f>
-        <v>55826.479800000001</v>
-      </c>
-      <c r="Q65" s="344">
-        <f>C31*N65+C32*O65</f>
-        <v>1674.794394</v>
-      </c>
-      <c r="R65" s="344">
-        <f>(-C28*O65-C29*(P65+Q65)+C30-G27-C32*O65/5)*(1-C11)</f>
-        <v>-15915.246846274573</v>
-      </c>
-      <c r="S65" s="344">
-        <f>C9+C20+R65</f>
-        <v>5040.0522770554253</v>
-      </c>
-      <c r="T65" s="344">
-        <f>C8+L65*N65/C7</f>
-        <v>2868.1402629999998</v>
-      </c>
-      <c r="U65" s="345">
-        <f>S65/T65/C10-1</f>
-        <v>-0.56608502083840517</v>
-      </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B66" s="342">
-        <v>1</v>
-      </c>
-      <c r="C66" s="343">
-        <f>+U82</f>
-        <v>-4.8899983703089123E-2</v>
-      </c>
-      <c r="D66" s="343">
-        <f>+U83</f>
-        <v>-8.8862258859609744E-2</v>
-      </c>
-      <c r="E66" s="343">
-        <f>+U84</f>
-        <v>-0.10762115800471683</v>
-      </c>
-      <c r="F66" s="343">
-        <f>+U85</f>
-        <v>-0.1256303603163561</v>
-      </c>
-      <c r="G66" s="343">
-        <f>+U86</f>
-        <v>-0.15957253526716442</v>
-      </c>
-      <c r="L66" s="329">
-        <f>$B62</f>
-        <v>0</v>
-      </c>
-      <c r="M66" s="329">
-        <f>G$61</f>
-        <v>0.4</v>
-      </c>
-      <c r="N66" s="344">
-        <f>C15*(1+M66)*C18</f>
-        <v>120241.64879999998</v>
-      </c>
-      <c r="O66" s="344">
-        <f>C26*(1-L66)*N66</f>
-        <v>60120.82439999999</v>
-      </c>
-      <c r="P66" s="344">
-        <f>(1-C26)*(1-L66)*N66</f>
-        <v>60120.82439999999</v>
-      </c>
-      <c r="Q66" s="344">
-        <f>C31*N66+C32*O66</f>
-        <v>1803.6247319999998</v>
-      </c>
-      <c r="R66" s="344">
-        <f>(-C28*O66-C29*(P66+Q66)+C30-G27-C32*O66/5)*(1-C11)</f>
-        <v>-17162.150449834153</v>
-      </c>
-      <c r="S66" s="344">
-        <f>C9+C20+R66</f>
-        <v>3793.1486734958453</v>
-      </c>
-      <c r="T66" s="344">
-        <f>C8+L66*N66/C7</f>
-        <v>2868.1402629999998</v>
-      </c>
-      <c r="U66" s="345">
-        <f>S66/T66/C10-1</f>
-        <v>-0.67343512782403614</v>
-      </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B67" s="346" t="s">
-        <v>518</v>
-      </c>
-      <c r="C67" s="347"/>
-      <c r="D67" s="347"/>
-      <c r="E67" s="347"/>
-      <c r="F67" s="347"/>
-      <c r="G67" s="347"/>
-      <c r="L67" s="329">
-        <f>$B63</f>
-        <v>0.25</v>
-      </c>
-      <c r="M67" s="329">
-        <f>C$61</f>
-        <v>0.1</v>
-      </c>
-      <c r="N67" s="344">
-        <f>C15*(1+M67)*C18</f>
-        <v>94475.581200000001</v>
-      </c>
-      <c r="O67" s="344">
-        <f>C26*(1-L67)*N67</f>
-        <v>35428.342949999998</v>
-      </c>
-      <c r="P67" s="344">
-        <f>(1-C26)*(1-L67)*N67</f>
-        <v>35428.342949999998</v>
-      </c>
-      <c r="Q67" s="344">
-        <f>C31*N67+C32*O67</f>
-        <v>1299.0392415000001</v>
-      </c>
-      <c r="R67" s="344">
-        <f>(-C28*O67-C29*(P67+Q67)+C30-G27-C32*O67/5)*(1-C11)</f>
-        <v>-10016.02993330891</v>
-      </c>
-      <c r="S67" s="344">
-        <f>C9+C20+R67</f>
-        <v>10939.269190021088</v>
-      </c>
-      <c r="T67" s="344">
-        <f>C8+L67*N67/C7</f>
-        <v>3524.2206879999999</v>
-      </c>
-      <c r="U67" s="345">
-        <f>S67/T67/C10-1</f>
-        <v>-0.23352992966901631</v>
-      </c>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="L68" s="329">
-        <f>$B63</f>
-        <v>0.25</v>
-      </c>
-      <c r="M68" s="329">
-        <f>D$61</f>
-        <v>0.2</v>
-      </c>
-      <c r="N68" s="344">
-        <f>C15*(1+M68)*C18</f>
-        <v>103064.27039999998</v>
-      </c>
-      <c r="O68" s="344">
-        <f>C26*(1-L68)*N68</f>
-        <v>38649.101399999992</v>
-      </c>
-      <c r="P68" s="344">
-        <f>(1-C26)*(1-L68)*N68</f>
-        <v>38649.101399999992</v>
-      </c>
-      <c r="Q68" s="344">
-        <f>C31*N68+C32*O68</f>
-        <v>1417.1337179999998</v>
-      </c>
-      <c r="R68" s="344">
-        <f>(-C28*O68-C29*(P68+Q68)+C30-G27-C32*O68/5)*(1-C11)</f>
-        <v>-10953.350836336993</v>
-      </c>
-      <c r="S68" s="344">
-        <f>C9+C20+R68</f>
-        <v>10001.948286993005</v>
-      </c>
-      <c r="T68" s="344">
-        <f>C8+L68*N68/C7</f>
-        <v>3583.8643629999997</v>
-      </c>
-      <c r="U68" s="345">
-        <f>S68/T68/C10-1</f>
-        <v>-0.31086703077303035</v>
-      </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B69" s="45" t="s">
-        <v>519</v>
-      </c>
-      <c r="L69" s="329">
-        <f>$B63</f>
-        <v>0.25</v>
-      </c>
-      <c r="M69" s="329">
-        <f>E$61</f>
-        <v>0.25</v>
-      </c>
-      <c r="N69" s="344">
-        <f>C15*(1+M69)*C18</f>
-        <v>107358.61500000001</v>
-      </c>
-      <c r="O69" s="344">
-        <f>C26*(1-L69)*N69</f>
-        <v>40259.480625000004</v>
-      </c>
-      <c r="P69" s="344">
-        <f>(1-C26)*(1-L69)*N69</f>
-        <v>40259.480625000004</v>
-      </c>
-      <c r="Q69" s="344">
-        <f>C31*N69+C32*O69</f>
-        <v>1476.1809562500002</v>
-      </c>
-      <c r="R69" s="344">
-        <f>(-C28*O69-C29*(P69+Q69)+C30-G27-C32*O69/5)*(1-C11)</f>
-        <v>-11422.011287851035</v>
-      </c>
-      <c r="S69" s="344">
-        <f>C9+C20+R69</f>
-        <v>9533.2878354789627</v>
-      </c>
-      <c r="T69" s="344">
-        <f>C8+L69*N69/C7</f>
-        <v>3613.6862004999998</v>
-      </c>
-      <c r="U69" s="345">
-        <f>S69/T69/C10-1</f>
-        <v>-0.3485782481475499</v>
-      </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B70" s="346" t="s">
-        <v>520</v>
-      </c>
-      <c r="C70" s="347"/>
-      <c r="D70" s="347"/>
-      <c r="E70" s="347"/>
-      <c r="F70" s="347"/>
-      <c r="G70" s="347"/>
-      <c r="H70" s="347"/>
-      <c r="I70" s="347"/>
-      <c r="J70" s="347"/>
-      <c r="L70" s="329">
-        <f>$B63</f>
-        <v>0.25</v>
-      </c>
-      <c r="M70" s="329">
-        <f>F$61</f>
-        <v>0.3</v>
-      </c>
-      <c r="N70" s="344">
-        <f>C15*(1+M70)*C18</f>
-        <v>111652.9596</v>
-      </c>
-      <c r="O70" s="344">
-        <f>C26*(1-L70)*N70</f>
-        <v>41869.859850000001</v>
-      </c>
-      <c r="P70" s="344">
-        <f>(1-C26)*(1-L70)*N70</f>
-        <v>41869.859850000001</v>
-      </c>
-      <c r="Q70" s="344">
-        <f>C31*N70+C32*O70</f>
-        <v>1535.2281945</v>
-      </c>
-      <c r="R70" s="344">
-        <f>(-C28*O70-C29*(P70+Q70)+C30-G27-C32*O70/5)*(1-C11)</f>
-        <v>-11890.671739365076</v>
-      </c>
-      <c r="S70" s="344">
-        <f>C9+C20+R70</f>
-        <v>9064.627383964922</v>
-      </c>
-      <c r="T70" s="344">
-        <f>C8+L70*N70/C7</f>
-        <v>3643.5080379999999</v>
-      </c>
-      <c r="U70" s="345">
-        <f>S70/T70/C10-1</f>
-        <v>-0.38567213860266036</v>
-      </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B71" s="346" t="s">
-        <v>521</v>
-      </c>
-      <c r="C71" s="347"/>
-      <c r="D71" s="347"/>
-      <c r="E71" s="347"/>
-      <c r="F71" s="347"/>
-      <c r="G71" s="347"/>
-      <c r="H71" s="347"/>
-      <c r="I71" s="347"/>
-      <c r="J71" s="347"/>
-      <c r="L71" s="329">
-        <f>$B63</f>
-        <v>0.25</v>
-      </c>
-      <c r="M71" s="329">
-        <f>G$61</f>
-        <v>0.4</v>
-      </c>
-      <c r="N71" s="344">
-        <f>C15*(1+M71)*C18</f>
-        <v>120241.64879999998</v>
-      </c>
-      <c r="O71" s="344">
-        <f>C26*(1-L71)*N71</f>
-        <v>45090.618299999995</v>
-      </c>
-      <c r="P71" s="344">
-        <f>(1-C26)*(1-L71)*N71</f>
-        <v>45090.618299999995</v>
-      </c>
-      <c r="Q71" s="344">
-        <f>C31*N71+C32*O71</f>
-        <v>1653.3226709999999</v>
-      </c>
-      <c r="R71" s="344">
-        <f>(-C28*O71-C29*(P71+Q71)+C30-G27-C32*O71/5)*(1-C11)</f>
-        <v>-12827.992642393161</v>
-      </c>
-      <c r="S71" s="344">
-        <f>C9+C20+R71</f>
-        <v>8127.306480936837</v>
-      </c>
-      <c r="T71" s="344">
-        <f>C8+L71*N71/C7</f>
-        <v>3703.1517129999997</v>
-      </c>
-      <c r="U71" s="345">
-        <f>S71/T71/C10-1</f>
-        <v>-0.45806759547250531</v>
-      </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B72" s="346" t="s">
-        <v>522</v>
-      </c>
-      <c r="C72" s="347"/>
-      <c r="D72" s="347"/>
-      <c r="E72" s="347"/>
-      <c r="F72" s="347"/>
-      <c r="G72" s="347"/>
-      <c r="H72" s="347"/>
-      <c r="I72" s="347"/>
-      <c r="J72" s="347"/>
-      <c r="L72" s="329">
-        <f>$B64</f>
-        <v>0.5</v>
-      </c>
-      <c r="M72" s="329">
-        <f>C$61</f>
-        <v>0.1</v>
-      </c>
-      <c r="N72" s="344">
-        <f>C15*(1+M72)*C18</f>
-        <v>94475.581200000001</v>
-      </c>
-      <c r="O72" s="344">
-        <f>C26*(1-L72)*N72</f>
-        <v>23618.8953</v>
-      </c>
-      <c r="P72" s="344">
-        <f>(1-C26)*(1-L72)*N72</f>
-        <v>23618.8953</v>
-      </c>
-      <c r="Q72" s="344">
-        <f>C31*N72+C32*O72</f>
-        <v>1180.944765</v>
-      </c>
-      <c r="R72" s="344">
-        <f>(-C28*O72-C29*(P72+Q72)+C30-G27-C32*O72/5)*(1-C11)</f>
-        <v>-6610.6202274624166</v>
-      </c>
-      <c r="S72" s="344">
-        <f>C9+C20+R72</f>
-        <v>14344.678895867582</v>
-      </c>
-      <c r="T72" s="344">
-        <f>C8+L72*N72/C7</f>
-        <v>4180.3011129999995</v>
-      </c>
-      <c r="U72" s="345">
-        <f>S72/T72/C10-1</f>
-        <v>-0.15266869279981787</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B73" s="346" t="s">
-        <v>523</v>
-      </c>
-      <c r="C73" s="347"/>
-      <c r="D73" s="347"/>
-      <c r="E73" s="347"/>
-      <c r="F73" s="347"/>
-      <c r="G73" s="347"/>
-      <c r="H73" s="347"/>
-      <c r="I73" s="347"/>
-      <c r="J73" s="347"/>
-      <c r="L73" s="329">
-        <f>$B64</f>
-        <v>0.5</v>
-      </c>
-      <c r="M73" s="329">
-        <f>D$61</f>
-        <v>0.2</v>
-      </c>
-      <c r="N73" s="344">
-        <f>C15*(1+M73)*C18</f>
-        <v>103064.27039999998</v>
-      </c>
-      <c r="O73" s="344">
-        <f>C26*(1-L73)*N73</f>
-        <v>25766.067599999995</v>
-      </c>
-      <c r="P73" s="344">
-        <f>(1-C26)*(1-L73)*N73</f>
-        <v>25766.067599999995</v>
-      </c>
-      <c r="Q73" s="344">
-        <f>C31*N73+C32*O73</f>
-        <v>1288.3033799999998</v>
-      </c>
-      <c r="R73" s="344">
-        <f>(-C28*O73-C29*(P73+Q73)+C30-G27-C32*O73/5)*(1-C11)</f>
-        <v>-7238.3584299589984</v>
-      </c>
-      <c r="S73" s="344">
-        <f>C9+C20+R73</f>
-        <v>13716.940693371</v>
-      </c>
-      <c r="T73" s="344">
-        <f>C8+L73*N73/C7</f>
-        <v>4299.588463</v>
-      </c>
-      <c r="U73" s="345">
-        <f>S73/T73/C10-1</f>
-        <v>-0.21222832785640933</v>
-      </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B74" s="346" t="s">
-        <v>524</v>
-      </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
-      <c r="G74" s="347"/>
-      <c r="H74" s="347"/>
-      <c r="I74" s="347"/>
-      <c r="J74" s="347"/>
-      <c r="L74" s="329">
-        <f>$B64</f>
-        <v>0.5</v>
-      </c>
-      <c r="M74" s="329">
-        <f>E$61</f>
-        <v>0.25</v>
-      </c>
-      <c r="N74" s="344">
-        <f>C15*(1+M74)*C18</f>
-        <v>107358.61500000001</v>
-      </c>
-      <c r="O74" s="344">
-        <f>C26*(1-L74)*N74</f>
-        <v>26839.653750000001</v>
-      </c>
-      <c r="P74" s="344">
-        <f>(1-C26)*(1-L74)*N74</f>
-        <v>26839.653750000001</v>
-      </c>
-      <c r="Q74" s="344">
-        <f>C31*N74+C32*O74</f>
-        <v>1341.9826875000001</v>
-      </c>
-      <c r="R74" s="344">
-        <f>(-C28*O74-C29*(P74+Q74)+C30-G27-C32*O74/5)*(1-C11)</f>
-        <v>-7552.2275312072907</v>
-      </c>
-      <c r="S74" s="344">
-        <f>C9+C20+R74</f>
-        <v>13403.071592122707</v>
-      </c>
-      <c r="T74" s="344">
-        <f>C8+L74*N74/C7</f>
-        <v>4359.2321379999994</v>
-      </c>
-      <c r="U74" s="345">
-        <f>S74/T74/C10-1</f>
-        <v>-0.24078578944999751</v>
-      </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B75" s="346" t="s">
-        <v>525</v>
-      </c>
-      <c r="C75" s="347"/>
-      <c r="D75" s="347"/>
-      <c r="E75" s="347"/>
-      <c r="F75" s="347"/>
-      <c r="G75" s="347"/>
-      <c r="H75" s="347"/>
-      <c r="I75" s="347"/>
-      <c r="J75" s="347"/>
-      <c r="L75" s="329">
-        <f>$B64</f>
-        <v>0.5</v>
-      </c>
-      <c r="M75" s="329">
-        <f>F$61</f>
-        <v>0.3</v>
-      </c>
-      <c r="N75" s="344">
-        <f>C15*(1+M75)*C18</f>
-        <v>111652.9596</v>
-      </c>
-      <c r="O75" s="344">
-        <f>C26*(1-L75)*N75</f>
-        <v>27913.2399</v>
-      </c>
-      <c r="P75" s="344">
-        <f>(1-C26)*(1-L75)*N75</f>
-        <v>27913.2399</v>
-      </c>
-      <c r="Q75" s="344">
-        <f>C31*N75+C32*O75</f>
-        <v>1395.6619950000002</v>
-      </c>
-      <c r="R75" s="344">
-        <f>(-C28*O75-C29*(P75+Q75)+C30-G27-C32*O75/5)*(1-C11)</f>
-        <v>-7866.096632455582</v>
-      </c>
-      <c r="S75" s="344">
-        <f>C9+C20+R75</f>
-        <v>13089.202490874417</v>
-      </c>
-      <c r="T75" s="344">
-        <f>C8+L75*N75/C7</f>
-        <v>4418.8758129999997</v>
-      </c>
-      <c r="U75" s="345">
-        <f>S75/T75/C10-1</f>
-        <v>-0.26857234367700999</v>
-      </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B76" s="346" t="s">
-        <v>526</v>
-      </c>
-      <c r="C76" s="347"/>
-      <c r="D76" s="347"/>
-      <c r="E76" s="347"/>
-      <c r="F76" s="347"/>
-      <c r="G76" s="347"/>
-      <c r="H76" s="347"/>
-      <c r="I76" s="347"/>
-      <c r="J76" s="347"/>
-      <c r="L76" s="329">
-        <f>$B64</f>
-        <v>0.5</v>
-      </c>
-      <c r="M76" s="329">
-        <f>G$61</f>
-        <v>0.4</v>
-      </c>
-      <c r="N76" s="344">
-        <f>C15*(1+M76)*C18</f>
-        <v>120241.64879999998</v>
-      </c>
-      <c r="O76" s="344">
-        <f>C26*(1-L76)*N76</f>
-        <v>30060.412199999995</v>
-      </c>
-      <c r="P76" s="344">
-        <f>(1-C26)*(1-L76)*N76</f>
-        <v>30060.412199999995</v>
-      </c>
-      <c r="Q76" s="344">
-        <f>C31*N76+C32*O76</f>
-        <v>1503.0206099999998</v>
-      </c>
-      <c r="R76" s="344">
-        <f>(-C28*O76-C29*(P76+Q76)+C30-G27-C32*O76/5)*(1-C11)</f>
-        <v>-8493.8348349521657</v>
-      </c>
-      <c r="S76" s="344">
-        <f>C9+C20+R76</f>
-        <v>12461.464288377832</v>
-      </c>
-      <c r="T76" s="344">
-        <f>C8+L76*N76/C7</f>
-        <v>4538.1631629999993</v>
-      </c>
-      <c r="U76" s="345">
-        <f>S76/T76/C10-1</f>
-        <v>-0.32195431159664711</v>
-      </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="L77" s="329">
-        <f>$B65</f>
-        <v>0.75</v>
-      </c>
-      <c r="M77" s="329">
-        <f>C$61</f>
-        <v>0.1</v>
-      </c>
-      <c r="N77" s="344">
-        <f>C15*(1+M77)*C18</f>
-        <v>94475.581200000001</v>
-      </c>
-      <c r="O77" s="344">
-        <f>C26*(1-L77)*N77</f>
-        <v>11809.44765</v>
-      </c>
-      <c r="P77" s="344">
-        <f>(1-C26)*(1-L77)*N77</f>
-        <v>11809.44765</v>
-      </c>
-      <c r="Q77" s="344">
-        <f>C31*N77+C32*O77</f>
-        <v>1062.8502885</v>
-      </c>
-      <c r="R77" s="344">
-        <f>(-C28*O77-C29*(P77+Q77)+C30-G27-C32*O77/5)*(1-C11)</f>
-        <v>-3205.2105216159212</v>
-      </c>
-      <c r="S77" s="344">
-        <f>C9+C20+R77</f>
-        <v>17750.088601714077</v>
-      </c>
-      <c r="T77" s="344">
-        <f>C8+L77*N77/C7</f>
-        <v>4836.3815379999996</v>
-      </c>
-      <c r="U77" s="345">
-        <f>S77/T77/C10-1</f>
-        <v>-9.3745954468974269E-2</v>
-      </c>
-    </row>
-    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="L78" s="329">
-        <f>$B65</f>
-        <v>0.75</v>
-      </c>
-      <c r="M78" s="329">
-        <f>D$61</f>
-        <v>0.2</v>
-      </c>
-      <c r="N78" s="344">
-        <f>C15*(1+M78)*C18</f>
-        <v>103064.27039999998</v>
-      </c>
-      <c r="O78" s="344">
-        <f>C26*(1-L78)*N78</f>
-        <v>12883.033799999997</v>
-      </c>
-      <c r="P78" s="344">
-        <f>(1-C26)*(1-L78)*N78</f>
-        <v>12883.033799999997</v>
-      </c>
-      <c r="Q78" s="344">
-        <f>C31*N78+C32*O78</f>
-        <v>1159.4730419999999</v>
-      </c>
-      <c r="R78" s="344">
-        <f>(-C28*O78-C29*(P78+Q78)+C30-G27-C32*O78/5)*(1-C11)</f>
-        <v>-3523.3660235810034</v>
-      </c>
-      <c r="S78" s="344">
-        <f>C9+C20+R78</f>
-        <v>17431.933099748996</v>
-      </c>
-      <c r="T78" s="344">
-        <f>C8+L78*N78/C7</f>
-        <v>5015.3125629999995</v>
-      </c>
-      <c r="U78" s="345">
-        <f>S78/T78/C10-1</f>
-        <v>-0.1417426447100798</v>
-      </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="L79" s="329">
-        <f>$B65</f>
-        <v>0.75</v>
-      </c>
-      <c r="M79" s="329">
-        <f>E$61</f>
-        <v>0.25</v>
-      </c>
-      <c r="N79" s="344">
-        <f>C15*(1+M79)*C18</f>
-        <v>107358.61500000001</v>
-      </c>
-      <c r="O79" s="344">
-        <f>C26*(1-L79)*N79</f>
-        <v>13419.826875000001</v>
-      </c>
-      <c r="P79" s="344">
-        <f>(1-C26)*(1-L79)*N79</f>
-        <v>13419.826875000001</v>
-      </c>
-      <c r="Q79" s="344">
-        <f>C31*N79+C32*O79</f>
-        <v>1207.78441875</v>
-      </c>
-      <c r="R79" s="344">
-        <f>(-C28*O79-C29*(P79+Q79)+C30-G27-C32*O79/5)*(1-C11)</f>
-        <v>-3682.4437745635464</v>
-      </c>
-      <c r="S79" s="344">
-        <f>C9+C20+R79</f>
-        <v>17272.85534876645</v>
-      </c>
-      <c r="T79" s="344">
-        <f>C8+L79*N79/C7</f>
-        <v>5104.7780755000003</v>
-      </c>
-      <c r="U79" s="345">
-        <f>S79/T79/C10-1</f>
-        <v>-0.16447921651927211</v>
-      </c>
-    </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="L80" s="329">
-        <f>$B65</f>
-        <v>0.75</v>
-      </c>
-      <c r="M80" s="329">
-        <f>F$61</f>
-        <v>0.3</v>
-      </c>
-      <c r="N80" s="344">
-        <f>C15*(1+M80)*C18</f>
-        <v>111652.9596</v>
-      </c>
-      <c r="O80" s="344">
-        <f>C26*(1-L80)*N80</f>
-        <v>13956.61995</v>
-      </c>
-      <c r="P80" s="344">
-        <f>(1-C26)*(1-L80)*N80</f>
-        <v>13956.61995</v>
-      </c>
-      <c r="Q80" s="344">
-        <f>C31*N80+C32*O80</f>
-        <v>1256.0957955000001</v>
-      </c>
-      <c r="R80" s="344">
-        <f>(-C28*O80-C29*(P80+Q80)+C30-G27-C32*O80/5)*(1-C11)</f>
-        <v>-3841.521525546088</v>
-      </c>
-      <c r="S80" s="344">
-        <f>C9+C20+R80</f>
-        <v>17113.777597783912</v>
-      </c>
-      <c r="T80" s="344">
-        <f>C8+L80*N80/C7</f>
-        <v>5194.2435879999994</v>
-      </c>
-      <c r="U80" s="345">
-        <f>S80/T80/C10-1</f>
-        <v>-0.18643256012018261</v>
-      </c>
-    </row>
-    <row r="81" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L81" s="329">
-        <f>$B65</f>
-        <v>0.75</v>
-      </c>
-      <c r="M81" s="329">
-        <f>G$61</f>
-        <v>0.4</v>
-      </c>
-      <c r="N81" s="344">
-        <f>C15*(1+M81)*C18</f>
-        <v>120241.64879999998</v>
-      </c>
-      <c r="O81" s="344">
-        <f>C26*(1-L81)*N81</f>
-        <v>15030.206099999998</v>
-      </c>
-      <c r="P81" s="344">
-        <f>(1-C26)*(1-L81)*N81</f>
-        <v>15030.206099999998</v>
-      </c>
-      <c r="Q81" s="344">
-        <f>C31*N81+C32*O81</f>
-        <v>1352.7185489999997</v>
-      </c>
-      <c r="R81" s="344">
-        <f>(-C28*O81-C29*(P81+Q81)+C30-G27-C32*O81/5)*(1-C11)</f>
-        <v>-4159.6770275111712</v>
-      </c>
-      <c r="S81" s="344">
-        <f>C9+C20+R81</f>
-        <v>16795.622095818828</v>
-      </c>
-      <c r="T81" s="344">
-        <f>C8+L81*N81/C7</f>
-        <v>5373.1746129999992</v>
-      </c>
-      <c r="U81" s="345">
-        <f>S81/T81/C10-1</f>
-        <v>-0.22814605546303257</v>
-      </c>
-    </row>
-    <row r="82" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L82" s="329">
-        <f>$B66</f>
-        <v>1</v>
-      </c>
-      <c r="M82" s="329">
-        <f>C$61</f>
-        <v>0.1</v>
-      </c>
-      <c r="N82" s="344">
-        <f>C15*(1+M82)*C18</f>
-        <v>94475.581200000001</v>
-      </c>
-      <c r="O82" s="344">
-        <f>C26*(1-L82)*N82</f>
-        <v>0</v>
-      </c>
-      <c r="P82" s="344">
-        <f>(1-C26)*(1-L82)*N82</f>
-        <v>0</v>
-      </c>
-      <c r="Q82" s="344">
-        <f>C31*N82+C32*O82</f>
-        <v>944.75581199999999</v>
-      </c>
-      <c r="R82" s="344">
-        <f>(-C28*O82-C29*(P82+Q82)+C30-G27-C32*O82/5)*(1-C11)</f>
-        <v>200.19918423057462</v>
-      </c>
-      <c r="S82" s="344">
-        <f>C9+C20+R82</f>
-        <v>21155.498307560574</v>
-      </c>
-      <c r="T82" s="344">
-        <f>C8+L82*N82/C7</f>
-        <v>5492.4619629999997</v>
-      </c>
-      <c r="U82" s="345">
-        <f>S82/T82/C10-1</f>
-        <v>-4.8899983703089123E-2</v>
-      </c>
-    </row>
-    <row r="83" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L83" s="329">
-        <f>$B66</f>
-        <v>1</v>
-      </c>
-      <c r="M83" s="329">
-        <f>D$61</f>
-        <v>0.2</v>
-      </c>
-      <c r="N83" s="344">
-        <f>C15*(1+M83)*C18</f>
-        <v>103064.27039999998</v>
-      </c>
-      <c r="O83" s="344">
-        <f>C26*(1-L83)*N83</f>
-        <v>0</v>
-      </c>
-      <c r="P83" s="344">
-        <f>(1-C26)*(1-L83)*N83</f>
-        <v>0</v>
-      </c>
-      <c r="Q83" s="344">
-        <f>C31*N83+C32*O83</f>
-        <v>1030.6427039999999</v>
-      </c>
-      <c r="R83" s="344">
-        <f>(-C28*O83-C29*(P83+Q83)+C30-G27-C32*O83/5)*(1-C11)</f>
-        <v>191.6263827969905</v>
-      </c>
-      <c r="S83" s="344">
-        <f>C9+C20+R83</f>
-        <v>21146.925506126987</v>
-      </c>
-      <c r="T83" s="344">
-        <f>C8+L83*N83/C7</f>
-        <v>5731.036662999999</v>
-      </c>
-      <c r="U83" s="345">
-        <f>S83/T83/C10-1</f>
-        <v>-8.8862258859609744E-2</v>
-      </c>
-    </row>
-    <row r="84" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L84" s="329">
-        <f>$B66</f>
-        <v>1</v>
-      </c>
-      <c r="M84" s="329">
-        <f>E$61</f>
-        <v>0.25</v>
-      </c>
-      <c r="N84" s="344">
-        <f>C15*(1+M84)*C18</f>
-        <v>107358.61500000001</v>
-      </c>
-      <c r="O84" s="344">
-        <f>C26*(1-L84)*N84</f>
-        <v>0</v>
-      </c>
-      <c r="P84" s="344">
-        <f>(1-C26)*(1-L84)*N84</f>
-        <v>0</v>
-      </c>
-      <c r="Q84" s="344">
-        <f>C31*N84+C32*O84</f>
-        <v>1073.5861500000001</v>
-      </c>
-      <c r="R84" s="344">
-        <f>(-C28*O84-C29*(P84+Q84)+C30-G27-C32*O84/5)*(1-C11)</f>
-        <v>187.33998208019847</v>
-      </c>
-      <c r="S84" s="344">
-        <f>C9+C20+R84</f>
-        <v>21142.639105410195</v>
-      </c>
-      <c r="T84" s="344">
-        <f>C8+L84*N84/C7</f>
-        <v>5850.3240129999995</v>
-      </c>
-      <c r="U84" s="345">
-        <f>S84/T84/C10-1</f>
-        <v>-0.10762115800471683</v>
-      </c>
-    </row>
-    <row r="85" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L85" s="329">
-        <f>$B66</f>
-        <v>1</v>
-      </c>
-      <c r="M85" s="329">
-        <f>F$61</f>
-        <v>0.3</v>
-      </c>
-      <c r="N85" s="344">
-        <f>C15*(1+M85)*C18</f>
-        <v>111652.9596</v>
-      </c>
-      <c r="O85" s="344">
-        <f>C26*(1-L85)*N85</f>
-        <v>0</v>
-      </c>
-      <c r="P85" s="344">
-        <f>(1-C26)*(1-L85)*N85</f>
-        <v>0</v>
-      </c>
-      <c r="Q85" s="344">
-        <f>C31*N85+C32*O85</f>
-        <v>1116.5295960000001</v>
-      </c>
-      <c r="R85" s="344">
-        <f>(-C28*O85-C29*(P85+Q85)+C30-G27-C32*O85/5)*(1-C11)</f>
-        <v>183.05358136340638</v>
-      </c>
-      <c r="S85" s="344">
-        <f>C9+C20+R85</f>
-        <v>21138.352704693403</v>
-      </c>
-      <c r="T85" s="344">
-        <f>C8+L85*N85/C7</f>
-        <v>5969.611363</v>
-      </c>
-      <c r="U85" s="345">
-        <f>S85/T85/C10-1</f>
-        <v>-0.1256303603163561</v>
-      </c>
-    </row>
-    <row r="86" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L86" s="329">
-        <f>$B66</f>
-        <v>1</v>
-      </c>
-      <c r="M86" s="329">
-        <f>G$61</f>
-        <v>0.4</v>
-      </c>
-      <c r="N86" s="344">
-        <f>C15*(1+M86)*C18</f>
-        <v>120241.64879999998</v>
-      </c>
-      <c r="O86" s="344">
-        <f>C26*(1-L86)*N86</f>
-        <v>0</v>
-      </c>
-      <c r="P86" s="344">
-        <f>(1-C26)*(1-L86)*N86</f>
-        <v>0</v>
-      </c>
-      <c r="Q86" s="344">
-        <f>C31*N86+C32*O86</f>
-        <v>1202.4164879999998</v>
-      </c>
-      <c r="R86" s="344">
-        <f>(-C28*O86-C29*(P86+Q86)+C30-G27-C32*O86/5)*(1-C11)</f>
-        <v>174.48077992982226</v>
-      </c>
-      <c r="S86" s="344">
-        <f>C9+C20+R86</f>
-        <v>21129.77990325982</v>
-      </c>
-      <c r="T86" s="344">
-        <f>C8+L86*N86/C7</f>
-        <v>6208.1860629999992</v>
-      </c>
-      <c r="U86" s="345">
-        <f>S86/T86/C10-1</f>
-        <v>-0.15957253526716442</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B76:J76"/>
-    <mergeCell ref="B71:J71"/>
-    <mergeCell ref="B75:J75"/>
-    <mergeCell ref="F57:J57"/>
-    <mergeCell ref="B73:J73"/>
-    <mergeCell ref="B74:J74"/>
-    <mergeCell ref="B70:J70"/>
-    <mergeCell ref="B72:J72"/>
-    <mergeCell ref="B67:G67"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:I67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="2" style="6" customWidth="1"/>
-    <col min="2" max="2" width="38" style="6" customWidth="1"/>
-    <col min="3" max="3" width="2" style="6" customWidth="1"/>
-    <col min="4" max="7" width="16" style="6" customWidth="1"/>
-    <col min="8" max="8" width="2" style="6" customWidth="1"/>
-    <col min="9" max="9" width="46" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:9" s="51" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="52" t="s">
-        <v>532</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="312" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="45" t="s">
-        <v>317</v>
-      </c>
-      <c r="D4" s="313" t="s">
-        <v>531</v>
-      </c>
-      <c r="I4" s="312"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="308" t="s">
-        <v>318</v>
-      </c>
-      <c r="C6" s="309"/>
-      <c r="D6" s="309"/>
-      <c r="E6" s="309"/>
-      <c r="F6" s="309"/>
-      <c r="G6" s="309"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="313" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" s="313" t="s">
-        <v>319</v>
-      </c>
-      <c r="F7" s="313" t="s">
-        <v>320</v>
-      </c>
-      <c r="G7" s="313" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="35" t="s">
-        <v>322</v>
-      </c>
-      <c r="D8" s="313" t="s">
-        <v>323</v>
-      </c>
-      <c r="E8" s="313" t="s">
-        <v>324</v>
-      </c>
-      <c r="F8" s="313" t="s">
-        <v>325</v>
-      </c>
-      <c r="G8" s="313" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="35" t="s">
-        <v>327</v>
-      </c>
-      <c r="D9" s="313" t="s">
-        <v>328</v>
-      </c>
-      <c r="E9" s="313" t="s">
-        <v>328</v>
-      </c>
-      <c r="F9" s="313" t="s">
-        <v>329</v>
-      </c>
-      <c r="G9" s="313" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="D10" s="313" t="s">
-        <v>332</v>
-      </c>
-      <c r="E10" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F10" s="313" t="s">
-        <v>332</v>
-      </c>
-      <c r="G10" s="313" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="D11" s="322">
-        <f>+DCF!H5</f>
-        <v>36</v>
-      </c>
-      <c r="E11" s="323">
-        <v>67.97</v>
-      </c>
-      <c r="F11" s="323">
-        <v>124.1</v>
-      </c>
-      <c r="G11" s="323">
-        <v>0.74</v>
-      </c>
-      <c r="I11" s="312" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="312" t="s">
-        <v>335</v>
-      </c>
-      <c r="D12" s="324" t="s">
-        <v>336</v>
-      </c>
-      <c r="E12" s="324" t="s">
-        <v>336</v>
-      </c>
-      <c r="F12" s="324" t="s">
-        <v>336</v>
-      </c>
-      <c r="G12" s="324" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="308" t="s">
-        <v>337</v>
-      </c>
-      <c r="C14" s="309"/>
-      <c r="D14" s="309"/>
-      <c r="E14" s="309"/>
-      <c r="F14" s="309"/>
-      <c r="G14" s="309"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="35" t="s">
-        <v>338</v>
-      </c>
-      <c r="D15" s="325">
-        <f>+DCF!C72/1000000</f>
-        <v>2868.1402629999998</v>
-      </c>
-      <c r="E15" s="326">
-        <v>1263.5999999999999</v>
-      </c>
-      <c r="F15" s="326">
-        <v>476</v>
-      </c>
-      <c r="G15" s="326">
-        <v>8284</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="35" t="s">
-        <v>339</v>
-      </c>
-      <c r="D16" s="326">
-        <v>0</v>
-      </c>
-      <c r="E16" s="326">
-        <v>0</v>
-      </c>
-      <c r="F16" s="326">
-        <v>0</v>
-      </c>
-      <c r="G16" s="326">
-        <v>0</v>
-      </c>
-      <c r="I16" s="312"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="45" t="s">
-        <v>340</v>
-      </c>
-      <c r="D17" s="327">
-        <f>+D15+D16</f>
-        <v>2868.1402629999998</v>
-      </c>
-      <c r="E17" s="327">
-        <f>+E15+E16</f>
-        <v>1263.5999999999999</v>
-      </c>
-      <c r="F17" s="327">
-        <f>+F15+F16</f>
-        <v>476</v>
-      </c>
-      <c r="G17" s="327">
-        <f>+G15+G16</f>
-        <v>8284</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="308" t="s">
-        <v>341</v>
-      </c>
-      <c r="C19" s="309"/>
-      <c r="D19" s="309"/>
-      <c r="E19" s="309"/>
-      <c r="F19" s="309"/>
-      <c r="G19" s="309"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="D20" s="320">
-        <f>+(FSM!F79+FSM!F88+FSM!F83+FSM!F90)/1000000</f>
-        <v>842.05469300000004</v>
-      </c>
-      <c r="E20" s="315">
-        <v>30</v>
-      </c>
-      <c r="F20" s="315">
-        <v>900</v>
-      </c>
-      <c r="G20" s="315">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="35" t="s">
-        <v>343</v>
-      </c>
-      <c r="D21" s="315">
-        <v>0</v>
-      </c>
-      <c r="E21" s="315">
-        <v>0</v>
-      </c>
-      <c r="F21" s="315">
-        <v>0</v>
-      </c>
-      <c r="G21" s="315">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="35" t="s">
-        <v>344</v>
-      </c>
-      <c r="D22" s="320">
-        <f>+D20+D21-(DCF!C65/1000000)</f>
-        <v>16941.003995999999</v>
-      </c>
-      <c r="E22" s="315">
-        <v>15000</v>
-      </c>
-      <c r="F22" s="315">
-        <v>4500</v>
-      </c>
-      <c r="G22" s="315">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="45" t="s">
-        <v>345</v>
-      </c>
-      <c r="D23" s="328">
-        <f>+D20+D21-D22</f>
-        <v>-16098.949302999999</v>
-      </c>
-      <c r="E23" s="328">
-        <f>+E20+E21-E22</f>
-        <v>-14970</v>
-      </c>
-      <c r="F23" s="328">
-        <f>+F20+F21-F22</f>
-        <v>-3600</v>
-      </c>
-      <c r="G23" s="328">
-        <f>+G20+G21-G22</f>
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="308" t="s">
-        <v>346</v>
-      </c>
-      <c r="C25" s="309"/>
-      <c r="D25" s="309"/>
-      <c r="E25" s="309"/>
-      <c r="F25" s="309"/>
-      <c r="G25" s="309"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="45" t="s">
-        <v>347</v>
-      </c>
-      <c r="D26" s="328">
-        <f>+D11*D17</f>
-        <v>103253.049468</v>
-      </c>
-      <c r="E26" s="328">
-        <f>+E11*E17</f>
-        <v>85886.891999999993</v>
-      </c>
-      <c r="F26" s="328">
-        <f>+F11*F17</f>
-        <v>59071.6</v>
-      </c>
-      <c r="G26" s="328">
-        <f>+G11*G17</f>
-        <v>6130.16</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="45" t="s">
-        <v>348</v>
-      </c>
-      <c r="D27" s="317">
-        <f>+D26+D23</f>
-        <v>87154.100164999996</v>
-      </c>
-      <c r="E27" s="317">
-        <f>+E26+E23</f>
-        <v>70916.891999999993</v>
-      </c>
-      <c r="F27" s="317">
-        <f>+F26+F23</f>
-        <v>55471.6</v>
-      </c>
-      <c r="G27" s="317">
-        <f>+G26+G23</f>
-        <v>7486.16</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="308" t="s">
-        <v>349</v>
-      </c>
-      <c r="C29" s="309"/>
-      <c r="D29" s="309"/>
-      <c r="E29" s="309"/>
-      <c r="F29" s="309"/>
-      <c r="G29" s="309"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="312" t="s">
-        <v>350</v>
-      </c>
-      <c r="D30" s="324" t="s">
-        <v>351</v>
-      </c>
-      <c r="E30" s="324" t="s">
-        <v>352</v>
-      </c>
-      <c r="F30" s="324" t="s">
-        <v>351</v>
-      </c>
-      <c r="G30" s="324" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="320">
-        <f>+FSM!F16/1000000</f>
-        <v>26844.075575999999</v>
-      </c>
-      <c r="E31" s="315">
-        <v>22920</v>
-      </c>
-      <c r="F31" s="315">
-        <v>13070</v>
-      </c>
-      <c r="G31" s="315">
-        <v>2820</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="320">
-        <f>+FSM!F37/1000000</f>
-        <v>15279.05955</v>
-      </c>
-      <c r="E32" s="315">
-        <v>10300</v>
-      </c>
-      <c r="F32" s="315">
-        <v>5300</v>
-      </c>
-      <c r="G32" s="315">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="D33" s="320">
-        <f>+FSM!F26/1000000</f>
-        <v>12960.33052</v>
-      </c>
-      <c r="E33" s="315">
-        <v>9300</v>
-      </c>
-      <c r="F33" s="315">
-        <v>4200</v>
-      </c>
-      <c r="G33" s="315">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="D34" s="320">
-        <f>+FSM!F35/1000000</f>
-        <v>11296.540287</v>
-      </c>
-      <c r="E34" s="315">
-        <v>9340</v>
-      </c>
-      <c r="F34" s="315">
-        <v>4320</v>
-      </c>
-      <c r="G34" s="315">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="312" t="s">
-        <v>353</v>
-      </c>
-      <c r="D35" s="329">
-        <f>+D32/D31</f>
-        <v>0.56917808574716855</v>
-      </c>
-      <c r="E35" s="329">
-        <f>+E32/E31</f>
-        <v>0.44938917975567189</v>
-      </c>
-      <c r="F35" s="329">
-        <f>+F32/F31</f>
-        <v>0.40550879877582252</v>
-      </c>
-      <c r="G35" s="329">
-        <f>+G32/G31</f>
-        <v>0.36170212765957449</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="312" t="s">
-        <v>354</v>
-      </c>
-      <c r="D36" s="324"/>
-      <c r="E36" s="324"/>
-      <c r="F36" s="324"/>
-      <c r="G36" s="324"/>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="308" t="s">
-        <v>355</v>
-      </c>
-      <c r="C38" s="309"/>
-      <c r="D38" s="309"/>
-      <c r="E38" s="309"/>
-      <c r="F38" s="309"/>
-      <c r="G38" s="309"/>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="35" t="s">
-        <v>356</v>
-      </c>
-      <c r="D39" s="318">
-        <f>IFERROR(D27/D31,"NM")</f>
-        <v>3.246679138503108</v>
-      </c>
-      <c r="E39" s="318">
-        <f>IFERROR(E27/E31,"NM")</f>
-        <v>3.0941052356020937</v>
-      </c>
-      <c r="F39" s="318">
-        <f>IFERROR(F27/F31,"NM")</f>
-        <v>4.2441928079571536</v>
-      </c>
-      <c r="G39" s="318">
-        <f>IFERROR(G27/G31,"NM")</f>
-        <v>2.6546666666666665</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B40" s="45" t="s">
-        <v>357</v>
-      </c>
-      <c r="D40" s="319">
-        <f>IFERROR(D27/D32,"NM")</f>
-        <v>5.7041534447714088</v>
-      </c>
-      <c r="E40" s="319">
-        <f>IFERROR(E27/E32,"NM")</f>
-        <v>6.8851351456310672</v>
-      </c>
-      <c r="F40" s="319">
-        <f>IFERROR(F27/F32,"NM")</f>
-        <v>10.46633962264151</v>
-      </c>
-      <c r="G40" s="319">
-        <f>IFERROR(G27/G32,"NM")</f>
-        <v>7.3393725490196076</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="35" t="s">
-        <v>358</v>
-      </c>
-      <c r="D41" s="318">
-        <f>IFERROR(D27/D33,"NM")</f>
-        <v>6.7246819076493738</v>
-      </c>
-      <c r="E41" s="318">
-        <f>IFERROR(E27/E33,"NM")</f>
-        <v>7.6254722580645149</v>
-      </c>
-      <c r="F41" s="318">
-        <f>IFERROR(F27/F33,"NM")</f>
-        <v>13.20752380952381</v>
-      </c>
-      <c r="G41" s="318">
-        <f>IFERROR(G27/G33,"NM")</f>
-        <v>11.51716923076923</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="45" t="s">
-        <v>359</v>
-      </c>
-      <c r="D42" s="319">
-        <f>IFERROR(D26/D34,"NM")</f>
-        <v>9.1402364657454527</v>
-      </c>
-      <c r="E42" s="319">
-        <f>IFERROR(E26/E34,"NM")</f>
-        <v>9.1955987152034258</v>
-      </c>
-      <c r="F42" s="319">
-        <f>IFERROR(F26/F34,"NM")</f>
-        <v>13.673981481481482</v>
-      </c>
-      <c r="G42" s="319">
-        <f>IFERROR(G26/G34,"NM")</f>
-        <v>18.86203076923077</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="308" t="s">
-        <v>360</v>
-      </c>
-      <c r="C44" s="309"/>
-      <c r="D44" s="309"/>
-      <c r="E44" s="309"/>
-      <c r="F44" s="309"/>
-      <c r="G44" s="309"/>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D45" s="45" t="s">
-        <v>361</v>
-      </c>
-      <c r="E45" s="45" t="s">
-        <v>362</v>
-      </c>
-      <c r="F45" s="45" t="s">
-        <v>363</v>
-      </c>
-      <c r="G45" s="45" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="35" t="s">
-        <v>365</v>
-      </c>
-      <c r="D46" s="318">
-        <f>IFERROR(AVERAGE(E39:G39),"NM")</f>
-        <v>3.330988236741971</v>
-      </c>
-      <c r="E46" s="318">
-        <f>IFERROR(AVERAGE(E40:G40),"NM")</f>
-        <v>8.2302824390973957</v>
-      </c>
-      <c r="F46" s="318">
-        <f>IFERROR(AVERAGE(E41:G41),"NM")</f>
-        <v>10.78338843278585</v>
-      </c>
-      <c r="G46" s="318">
-        <f>IFERROR(AVERAGE(E42:G42),"NM")</f>
-        <v>13.91053698863856</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="45" t="s">
-        <v>366</v>
-      </c>
-      <c r="D47" s="319">
-        <f>IFERROR(MEDIAN(E39:G39),"NM")</f>
-        <v>3.0941052356020937</v>
-      </c>
-      <c r="E47" s="319">
-        <f>IFERROR(MEDIAN(E40:G40),"NM")</f>
-        <v>7.3393725490196076</v>
-      </c>
-      <c r="F47" s="319">
-        <f>IFERROR(MEDIAN(E41:G41),"NM")</f>
-        <v>11.51716923076923</v>
-      </c>
-      <c r="G47" s="319">
-        <f>IFERROR(MEDIAN(E42:G42),"NM")</f>
-        <v>13.673981481481482</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D48" s="318">
-        <f>IFERROR(MAX(E39:G39),"NM")</f>
-        <v>4.2441928079571536</v>
-      </c>
-      <c r="E48" s="318">
-        <f>IFERROR(MAX(E40:G40),"NM")</f>
-        <v>10.46633962264151</v>
-      </c>
-      <c r="F48" s="318">
-        <f>IFERROR(MAX(E41:G41),"NM")</f>
-        <v>13.20752380952381</v>
-      </c>
-      <c r="G48" s="318">
-        <f>IFERROR(MAX(E42:G42),"NM")</f>
-        <v>18.86203076923077</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" s="318">
-        <f>IFERROR(MIN(E39:G39),"NM")</f>
-        <v>2.6546666666666665</v>
-      </c>
-      <c r="E49" s="318">
-        <f>IFERROR(MIN(E40:G40),"NM")</f>
-        <v>6.8851351456310672</v>
-      </c>
-      <c r="F49" s="318">
-        <f>IFERROR(MIN(E41:G41),"NM")</f>
-        <v>7.6254722580645149</v>
-      </c>
-      <c r="G49" s="318">
-        <f>IFERROR(MIN(E42:G42),"NM")</f>
-        <v>9.1955987152034258</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B51" s="308" t="s">
-        <v>367</v>
-      </c>
-      <c r="C51" s="309"/>
-      <c r="D51" s="309"/>
-      <c r="E51" s="309"/>
-      <c r="F51" s="309"/>
-      <c r="G51" s="309"/>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="45" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="35" t="s">
-        <v>369</v>
-      </c>
-      <c r="D53" s="318">
-        <f>+E47</f>
-        <v>7.3393725490196076</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="35" t="s">
-        <v>370</v>
-      </c>
-      <c r="D54" s="316">
-        <f>+D32</f>
-        <v>15279.05955</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B55" s="35" t="s">
-        <v>371</v>
-      </c>
-      <c r="D55" s="316">
-        <f>+D53*D54</f>
-        <v>112138.71023610588</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B56" s="35" t="s">
-        <v>372</v>
-      </c>
-      <c r="D56" s="316">
-        <f>-D23</f>
-        <v>16098.949302999999</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="35" t="s">
-        <v>373</v>
-      </c>
-      <c r="D57" s="316">
-        <f>+D55+D56</f>
-        <v>128237.65953910588</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B58" s="45" t="s">
-        <v>374</v>
-      </c>
-      <c r="D58" s="321">
-        <f>+D57/D17</f>
-        <v>44.711083761633276</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B60" s="45" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B61" s="35" t="s">
-        <v>376</v>
-      </c>
-      <c r="D61" s="318">
-        <f>+G47</f>
-        <v>13.673981481481482</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B62" s="35" t="s">
-        <v>377</v>
-      </c>
-      <c r="D62" s="316">
-        <f>+D34</f>
-        <v>11296.540287</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B63" s="45" t="s">
-        <v>374</v>
-      </c>
-      <c r="D63" s="321">
-        <f>+D61*D62/D17</f>
-        <v>53.856739393797042</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B65" s="45" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B66" s="35" t="s">
-        <v>379</v>
-      </c>
-      <c r="D66" s="318">
-        <f>+E40</f>
-        <v>6.8851351456310672</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B67" s="45" t="s">
-        <v>374</v>
-      </c>
-      <c r="D67" s="321">
-        <f>(D66*D32-D23)/D17</f>
         <v>42.291285669558278</v>
       </c>
     </row>
